--- a/template_examples/standard_parameters_example.xlsx
+++ b/template_examples/standard_parameters_example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JanBaumeister\Documents\GitHub\SESMG\template_examples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FranziskaKoert\Documents\Github\SESMG-dev-20260709\template_examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2900A2A2-B837-4A76-AB33-C40043DBB0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1A14DF-44DA-48BD-9391-3326DA05DCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{D48BE4BC-BA48-4DC0-B3DF-D04B8CFD99C7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="6" xr2:uid="{D48BE4BC-BA48-4DC0-B3DF-D04B8CFD99C7}"/>
   </bookViews>
   <sheets>
     <sheet name="energysystem" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="379">
   <si>
     <t>start date</t>
   </si>
@@ -1156,6 +1156,33 @@
   </si>
   <si>
     <t>dc ac ratio</t>
+  </si>
+  <si>
+    <t>hydrogen bus combined heat and power central</t>
+  </si>
+  <si>
+    <t>electricity bus combined heat and power natural gas hydrogen central</t>
+  </si>
+  <si>
+    <t>combined heat and power natural gas hydrogen central</t>
+  </si>
+  <si>
+    <t>natural_gas_hydrogen_CHP</t>
+  </si>
+  <si>
+    <t>GenericTwoInputTransformer</t>
+  </si>
+  <si>
+    <t>electricity combined heat and power natural gas hydrogen central link central</t>
+  </si>
+  <si>
+    <t>variable input costs 2</t>
+  </si>
+  <si>
+    <t>input2 / input</t>
+  </si>
+  <si>
+    <t>variable input constraint costs 2</t>
   </si>
 </sst>
 </file>
@@ -1214,7 +1241,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1293,6 +1320,12 @@
         <bgColor rgb="FFDAE3F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -1364,7 +1397,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1392,12 +1425,48 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 3" xfId="1" xr:uid="{3EB3DAA0-9F71-48CB-8FEA-1E1CAF40E04C}"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="28">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1493,6 +1562,27 @@
       <fill>
         <patternFill>
           <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1849,19 +1939,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9349B1DA-DD91-4E08-AB6A-4F16A6735056}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6328125" customWidth="1"/>
-    <col min="6" max="6" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1893,7 +1983,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -1925,7 +2015,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>40909</v>
       </c>
@@ -1965,12 +2055,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0876A1A-D601-4F49-AE30-77EB630A1DC1}">
   <dimension ref="A1:D116"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -1984,7 +2074,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -1998,7 +2088,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>144</v>
       </c>
@@ -2012,7 +2102,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1919</v>
       </c>
@@ -2026,7 +2116,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1920</v>
       </c>
@@ -2040,7 +2130,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1921</v>
       </c>
@@ -2054,7 +2144,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1922</v>
       </c>
@@ -2068,7 +2158,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1923</v>
       </c>
@@ -2082,7 +2172,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1924</v>
       </c>
@@ -2096,7 +2186,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1925</v>
       </c>
@@ -2110,7 +2200,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1926</v>
       </c>
@@ -2124,7 +2214,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1927</v>
       </c>
@@ -2138,7 +2228,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1928</v>
       </c>
@@ -2152,7 +2242,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1929</v>
       </c>
@@ -2166,7 +2256,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1930</v>
       </c>
@@ -2180,7 +2270,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1931</v>
       </c>
@@ -2194,7 +2284,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1932</v>
       </c>
@@ -2208,7 +2298,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1933</v>
       </c>
@@ -2222,7 +2312,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1934</v>
       </c>
@@ -2236,7 +2326,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1935</v>
       </c>
@@ -2250,7 +2340,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1936</v>
       </c>
@@ -2264,7 +2354,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1937</v>
       </c>
@@ -2278,7 +2368,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1938</v>
       </c>
@@ -2292,7 +2382,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1939</v>
       </c>
@@ -2306,7 +2396,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1940</v>
       </c>
@@ -2320,7 +2410,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1941</v>
       </c>
@@ -2334,7 +2424,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1942</v>
       </c>
@@ -2348,7 +2438,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1943</v>
       </c>
@@ -2362,7 +2452,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1944</v>
       </c>
@@ -2376,7 +2466,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1945</v>
       </c>
@@ -2390,7 +2480,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1946</v>
       </c>
@@ -2404,7 +2494,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1947</v>
       </c>
@@ -2418,7 +2508,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1948</v>
       </c>
@@ -2432,7 +2522,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1949</v>
       </c>
@@ -2446,7 +2536,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1950</v>
       </c>
@@ -2460,7 +2550,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1951</v>
       </c>
@@ -2474,7 +2564,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1952</v>
       </c>
@@ -2488,7 +2578,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1953</v>
       </c>
@@ -2502,7 +2592,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1954</v>
       </c>
@@ -2516,7 +2606,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1955</v>
       </c>
@@ -2530,7 +2620,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1956</v>
       </c>
@@ -2544,7 +2634,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1957</v>
       </c>
@@ -2558,7 +2648,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1958</v>
       </c>
@@ -2572,7 +2662,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1959</v>
       </c>
@@ -2586,7 +2676,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1960</v>
       </c>
@@ -2600,7 +2690,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1961</v>
       </c>
@@ -2614,7 +2704,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1962</v>
       </c>
@@ -2628,7 +2718,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1963</v>
       </c>
@@ -2642,7 +2732,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1964</v>
       </c>
@@ -2656,7 +2746,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1965</v>
       </c>
@@ -2670,7 +2760,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1966</v>
       </c>
@@ -2684,7 +2774,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1967</v>
       </c>
@@ -2698,7 +2788,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1968</v>
       </c>
@@ -2712,7 +2802,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1969</v>
       </c>
@@ -2726,7 +2816,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1970</v>
       </c>
@@ -2740,7 +2830,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1971</v>
       </c>
@@ -2754,7 +2844,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1972</v>
       </c>
@@ -2768,7 +2858,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1973</v>
       </c>
@@ -2782,7 +2872,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1974</v>
       </c>
@@ -2796,7 +2886,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1975</v>
       </c>
@@ -2810,7 +2900,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1976</v>
       </c>
@@ -2824,7 +2914,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1977</v>
       </c>
@@ -2838,7 +2928,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1978</v>
       </c>
@@ -2852,7 +2942,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1979</v>
       </c>
@@ -2866,7 +2956,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1980</v>
       </c>
@@ -2880,7 +2970,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1981</v>
       </c>
@@ -2894,7 +2984,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1982</v>
       </c>
@@ -2908,7 +2998,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1983</v>
       </c>
@@ -2922,7 +3012,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1984</v>
       </c>
@@ -2936,7 +3026,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1985</v>
       </c>
@@ -2950,7 +3040,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1986</v>
       </c>
@@ -2964,7 +3054,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1987</v>
       </c>
@@ -2978,7 +3068,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1988</v>
       </c>
@@ -2992,7 +3082,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1989</v>
       </c>
@@ -3006,7 +3096,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1990</v>
       </c>
@@ -3020,7 +3110,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1991</v>
       </c>
@@ -3034,7 +3124,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1992</v>
       </c>
@@ -3048,7 +3138,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1993</v>
       </c>
@@ -3062,7 +3152,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1994</v>
       </c>
@@ -3076,7 +3166,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1995</v>
       </c>
@@ -3090,7 +3180,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1996</v>
       </c>
@@ -3104,7 +3194,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1997</v>
       </c>
@@ -3118,7 +3208,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1998</v>
       </c>
@@ -3132,7 +3222,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1999</v>
       </c>
@@ -3146,7 +3236,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>2000</v>
       </c>
@@ -3160,7 +3250,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>2001</v>
       </c>
@@ -3174,7 +3264,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>2002</v>
       </c>
@@ -3188,7 +3278,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>2003</v>
       </c>
@@ -3202,7 +3292,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>2004</v>
       </c>
@@ -3216,7 +3306,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>2005</v>
       </c>
@@ -3230,7 +3320,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>2006</v>
       </c>
@@ -3244,7 +3334,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>2007</v>
       </c>
@@ -3258,7 +3348,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>2008</v>
       </c>
@@ -3272,7 +3362,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>2009</v>
       </c>
@@ -3286,7 +3376,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>2010</v>
       </c>
@@ -3300,7 +3390,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>2011</v>
       </c>
@@ -3314,7 +3404,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>2012</v>
       </c>
@@ -3328,7 +3418,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>2013</v>
       </c>
@@ -3342,7 +3432,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>2014</v>
       </c>
@@ -3356,7 +3446,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>2015</v>
       </c>
@@ -3370,7 +3460,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>2016</v>
       </c>
@@ -3384,7 +3474,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>2017</v>
       </c>
@@ -3398,7 +3488,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>2018</v>
       </c>
@@ -3412,7 +3502,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>2019</v>
       </c>
@@ -3426,7 +3516,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>2020</v>
       </c>
@@ -3440,7 +3530,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>2021</v>
       </c>
@@ -3454,7 +3544,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>2022</v>
       </c>
@@ -3468,7 +3558,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>2023</v>
       </c>
@@ -3482,7 +3572,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>2024</v>
       </c>
@@ -3496,7 +3586,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>2025</v>
       </c>
@@ -3510,7 +3600,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>325</v>
       </c>
@@ -3524,7 +3614,7 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>326</v>
       </c>
@@ -3538,7 +3628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>163</v>
       </c>
@@ -3552,7 +3642,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>327</v>
       </c>
@@ -3566,7 +3656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>164</v>
       </c>
@@ -3580,7 +3670,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>328</v>
       </c>
@@ -3612,20 +3702,20 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EEE9DEA-E38F-C741-B378-A7CB5600BE5E}">
   <dimension ref="A1:O32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>329</v>
       </c>
@@ -3672,7 +3762,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>356</v>
       </c>
@@ -3719,7 +3809,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>337</v>
       </c>
@@ -3766,7 +3856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>338</v>
       </c>
@@ -3813,7 +3903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>339</v>
       </c>
@@ -3860,7 +3950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>340</v>
       </c>
@@ -3907,7 +3997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>341</v>
       </c>
@@ -3954,7 +4044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>342</v>
       </c>
@@ -4001,7 +4091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>343</v>
       </c>
@@ -4048,7 +4138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>344</v>
       </c>
@@ -4095,7 +4185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>345</v>
       </c>
@@ -4142,7 +4232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>346</v>
       </c>
@@ -4189,7 +4279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>347</v>
       </c>
@@ -4236,7 +4326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>348</v>
       </c>
@@ -4283,7 +4373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
         <v>350</v>
       </c>
@@ -4330,7 +4420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>357</v>
       </c>
@@ -4377,7 +4467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>358</v>
       </c>
@@ -4424,7 +4514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
         <v>359</v>
       </c>
@@ -4471,7 +4561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
         <v>360</v>
       </c>
@@ -4518,7 +4608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="20" t="s">
         <v>351</v>
       </c>
@@ -4565,7 +4655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
         <v>361</v>
       </c>
@@ -4612,7 +4702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
         <v>362</v>
       </c>
@@ -4659,7 +4749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="20" t="s">
         <v>363</v>
       </c>
@@ -4706,7 +4796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
         <v>352</v>
       </c>
@@ -4753,7 +4843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
         <v>364</v>
       </c>
@@ -4800,7 +4890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
         <v>353</v>
       </c>
@@ -4847,7 +4937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="20" t="s">
         <v>365</v>
       </c>
@@ -4894,7 +4984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="20" t="s">
         <v>366</v>
       </c>
@@ -4941,7 +5031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="20" t="s">
         <v>367</v>
       </c>
@@ -4988,7 +5078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="20" t="s">
         <v>368</v>
       </c>
@@ -5033,7 +5123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>354</v>
       </c>
@@ -5080,7 +5170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>355</v>
       </c>
@@ -5136,13 +5226,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6075F4E-6449-42F6-B0A2-E3B463F49D3C}">
-  <dimension ref="A1:I39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="53.08984375" customWidth="1"/>
+    <col min="1" max="1" width="65.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -5171,7 +5261,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -5200,7 +5290,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -5229,7 +5319,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -5258,7 +5348,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -5287,7 +5377,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -5316,7 +5406,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -5345,7 +5435,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -5374,7 +5464,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -5403,7 +5493,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -5432,7 +5522,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -5461,7 +5551,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -5490,7 +5580,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -5519,7 +5609,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -5548,7 +5638,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -5577,7 +5667,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -5606,7 +5696,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -5635,7 +5725,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -5664,7 +5754,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -5693,7 +5783,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -5722,7 +5812,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -5751,7 +5841,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -5780,7 +5870,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -5809,7 +5899,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -5838,7 +5928,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -5867,7 +5957,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -5896,7 +5986,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -5925,7 +6015,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -5954,7 +6044,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>51</v>
       </c>
@@ -5983,7 +6073,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>52</v>
       </c>
@@ -6012,7 +6102,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -6041,7 +6131,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>54</v>
       </c>
@@ -6070,7 +6160,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>55</v>
       </c>
@@ -6099,7 +6189,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -6128,7 +6218,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>57</v>
       </c>
@@ -6157,7 +6247,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>58</v>
       </c>
@@ -6186,7 +6276,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>59</v>
       </c>
@@ -6215,7 +6305,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>61</v>
       </c>
@@ -6244,7 +6334,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>62</v>
       </c>
@@ -6273,22 +6363,93 @@
         <v>12</v>
       </c>
     </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="B40" s="25">
+        <v>1</v>
+      </c>
+      <c r="C40" s="25">
+        <v>0</v>
+      </c>
+      <c r="D40" s="25">
+        <v>1</v>
+      </c>
+      <c r="E40" s="25">
+        <v>0</v>
+      </c>
+      <c r="F40" s="25">
+        <v>0.15620000000000001</v>
+      </c>
+      <c r="G40" s="25">
+        <v>0</v>
+      </c>
+      <c r="H40" s="25">
+        <v>44</v>
+      </c>
+      <c r="I40" s="25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="25" t="s">
+        <v>371</v>
+      </c>
+      <c r="B41" s="25">
+        <v>1</v>
+      </c>
+      <c r="C41" s="25">
+        <v>1</v>
+      </c>
+      <c r="D41" s="25">
+        <v>0</v>
+      </c>
+      <c r="E41" s="25">
+        <v>-6.8199999999999997E-2</v>
+      </c>
+      <c r="F41" s="25">
+        <v>0</v>
+      </c>
+      <c r="G41" s="25">
+        <v>-140</v>
+      </c>
+      <c r="H41" s="25">
+        <v>0</v>
+      </c>
+      <c r="I41" s="25" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B3:B22 B24:B35">
-    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B39">
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="6" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:H39">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="5" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40:B41">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40:H41">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6300,13 +6461,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A343EB-B652-4B18-B41E-28ABD2CDDDDD}">
   <dimension ref="A1:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -6338,7 +6499,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>356</v>
       </c>
@@ -6370,7 +6531,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -6402,7 +6563,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -6434,7 +6595,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -6466,7 +6627,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>76</v>
       </c>
@@ -6498,7 +6659,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -6530,7 +6691,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -6562,7 +6723,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -6594,7 +6755,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -6626,7 +6787,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>86</v>
       </c>
@@ -6658,7 +6819,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>88</v>
       </c>
@@ -6690,7 +6851,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>90</v>
       </c>
@@ -6722,7 +6883,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -6754,7 +6915,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -6786,7 +6947,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -6818,7 +6979,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -6850,7 +7011,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -6882,7 +7043,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -6914,7 +7075,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>101</v>
       </c>
@@ -6946,7 +7107,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -6978,7 +7139,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>103</v>
       </c>
@@ -7010,7 +7171,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>104</v>
       </c>
@@ -7042,7 +7203,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>105</v>
       </c>
@@ -7074,7 +7235,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>106</v>
       </c>
@@ -7106,7 +7267,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>107</v>
       </c>
@@ -7138,7 +7299,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>108</v>
       </c>
@@ -7170,7 +7331,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>109</v>
       </c>
@@ -7202,7 +7363,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>110</v>
       </c>
@@ -7234,7 +7395,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>111</v>
       </c>
@@ -7266,7 +7427,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>113</v>
       </c>
@@ -7298,7 +7459,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>114</v>
       </c>
@@ -7330,7 +7491,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>115</v>
       </c>
@@ -7371,12 +7532,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99D5AF32-1322-42FA-A3FF-C17883258B40}">
   <dimension ref="A1:Z110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="25" max="25" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>117</v>
       </c>
@@ -7456,7 +7617,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>356</v>
       </c>
@@ -7536,7 +7697,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>144</v>
       </c>
@@ -7616,7 +7777,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1919</v>
       </c>
@@ -7696,7 +7857,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1920</v>
       </c>
@@ -7776,7 +7937,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1921</v>
       </c>
@@ -7856,7 +8017,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1922</v>
       </c>
@@ -7936,7 +8097,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1923</v>
       </c>
@@ -8016,7 +8177,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1924</v>
       </c>
@@ -8096,7 +8257,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1925</v>
       </c>
@@ -8176,7 +8337,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1926</v>
       </c>
@@ -8256,7 +8417,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1927</v>
       </c>
@@ -8336,7 +8497,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1928</v>
       </c>
@@ -8416,7 +8577,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1929</v>
       </c>
@@ -8496,7 +8657,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1930</v>
       </c>
@@ -8576,7 +8737,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1931</v>
       </c>
@@ -8656,7 +8817,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1932</v>
       </c>
@@ -8736,7 +8897,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1933</v>
       </c>
@@ -8816,7 +8977,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1934</v>
       </c>
@@ -8896,7 +9057,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1935</v>
       </c>
@@ -8976,7 +9137,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1936</v>
       </c>
@@ -9056,7 +9217,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1937</v>
       </c>
@@ -9136,7 +9297,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1938</v>
       </c>
@@ -9216,7 +9377,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1939</v>
       </c>
@@ -9296,7 +9457,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1940</v>
       </c>
@@ -9376,7 +9537,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1941</v>
       </c>
@@ -9456,7 +9617,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1942</v>
       </c>
@@ -9536,7 +9697,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1943</v>
       </c>
@@ -9616,7 +9777,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1944</v>
       </c>
@@ -9696,7 +9857,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1945</v>
       </c>
@@ -9776,7 +9937,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1946</v>
       </c>
@@ -9856,7 +10017,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1947</v>
       </c>
@@ -9936,7 +10097,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1948</v>
       </c>
@@ -10016,7 +10177,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1949</v>
       </c>
@@ -10096,7 +10257,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1950</v>
       </c>
@@ -10176,7 +10337,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1951</v>
       </c>
@@ -10256,7 +10417,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1952</v>
       </c>
@@ -10336,7 +10497,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1953</v>
       </c>
@@ -10416,7 +10577,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1954</v>
       </c>
@@ -10496,7 +10657,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1955</v>
       </c>
@@ -10576,7 +10737,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1956</v>
       </c>
@@ -10656,7 +10817,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1957</v>
       </c>
@@ -10736,7 +10897,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1958</v>
       </c>
@@ -10816,7 +10977,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1959</v>
       </c>
@@ -10896,7 +11057,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1960</v>
       </c>
@@ -10976,7 +11137,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1961</v>
       </c>
@@ -11056,7 +11217,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1962</v>
       </c>
@@ -11136,7 +11297,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1963</v>
       </c>
@@ -11216,7 +11377,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1964</v>
       </c>
@@ -11296,7 +11457,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1965</v>
       </c>
@@ -11376,7 +11537,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1966</v>
       </c>
@@ -11456,7 +11617,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1967</v>
       </c>
@@ -11536,7 +11697,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1968</v>
       </c>
@@ -11616,7 +11777,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1969</v>
       </c>
@@ -11696,7 +11857,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1970</v>
       </c>
@@ -11776,7 +11937,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1971</v>
       </c>
@@ -11856,7 +12017,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1972</v>
       </c>
@@ -11936,7 +12097,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1973</v>
       </c>
@@ -12016,7 +12177,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1974</v>
       </c>
@@ -12096,7 +12257,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1975</v>
       </c>
@@ -12176,7 +12337,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1976</v>
       </c>
@@ -12256,7 +12417,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1977</v>
       </c>
@@ -12336,7 +12497,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1978</v>
       </c>
@@ -12416,7 +12577,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1979</v>
       </c>
@@ -12496,7 +12657,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1980</v>
       </c>
@@ -12576,7 +12737,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1981</v>
       </c>
@@ -12656,7 +12817,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1982</v>
       </c>
@@ -12736,7 +12897,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1983</v>
       </c>
@@ -12816,7 +12977,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1984</v>
       </c>
@@ -12896,7 +13057,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1985</v>
       </c>
@@ -12976,7 +13137,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1986</v>
       </c>
@@ -13056,7 +13217,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1987</v>
       </c>
@@ -13136,7 +13297,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1988</v>
       </c>
@@ -13216,7 +13377,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1989</v>
       </c>
@@ -13296,7 +13457,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1990</v>
       </c>
@@ -13376,7 +13537,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1991</v>
       </c>
@@ -13456,7 +13617,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1992</v>
       </c>
@@ -13536,7 +13697,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1993</v>
       </c>
@@ -13616,7 +13777,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1994</v>
       </c>
@@ -13696,7 +13857,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1995</v>
       </c>
@@ -13776,7 +13937,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1996</v>
       </c>
@@ -13856,7 +14017,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1997</v>
       </c>
@@ -13936,7 +14097,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1998</v>
       </c>
@@ -14016,7 +14177,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1999</v>
       </c>
@@ -14096,7 +14257,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>2000</v>
       </c>
@@ -14176,7 +14337,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>2001</v>
       </c>
@@ -14256,7 +14417,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>2002</v>
       </c>
@@ -14336,7 +14497,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>2003</v>
       </c>
@@ -14416,7 +14577,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>2004</v>
       </c>
@@ -14496,7 +14657,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>2005</v>
       </c>
@@ -14576,7 +14737,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>2006</v>
       </c>
@@ -14656,7 +14817,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>2007</v>
       </c>
@@ -14736,7 +14897,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>2008</v>
       </c>
@@ -14816,7 +14977,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>2009</v>
       </c>
@@ -14896,7 +15057,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>2010</v>
       </c>
@@ -14976,7 +15137,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>2011</v>
       </c>
@@ -15056,7 +15217,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>2012</v>
       </c>
@@ -15136,7 +15297,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>2013</v>
       </c>
@@ -15216,7 +15377,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>2014</v>
       </c>
@@ -15296,7 +15457,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>2015</v>
       </c>
@@ -15376,7 +15537,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>2016</v>
       </c>
@@ -15456,7 +15617,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>2017</v>
       </c>
@@ -15536,7 +15697,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>2018</v>
       </c>
@@ -15616,7 +15777,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>2019</v>
       </c>
@@ -15696,7 +15857,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>2020</v>
       </c>
@@ -15776,7 +15937,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>2021</v>
       </c>
@@ -15856,7 +16017,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>2022</v>
       </c>
@@ -15936,7 +16097,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>2023</v>
       </c>
@@ -16016,7 +16177,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>2024</v>
       </c>
@@ -16096,7 +16257,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>2025</v>
       </c>
@@ -16178,7 +16339,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3:A110">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16189,9 +16350,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0755075B-2E65-410D-A27F-07A269EC3FA7}">
   <dimension ref="A1:W3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -16262,7 +16423,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -16333,7 +16494,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>158</v>
       </c>
@@ -16412,15 +16573,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865B2AF4-2CF4-4093-8D70-C931333F20A4}">
   <dimension ref="A1:AF7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.453125" customWidth="1"/>
-    <col min="25" max="25" width="20.6328125" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" customWidth="1"/>
+    <col min="25" max="25" width="20.6640625" customWidth="1"/>
     <col min="32" max="32" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>159</v>
       </c>
@@ -16518,7 +16679,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -16616,7 +16777,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>187</v>
       </c>
@@ -16714,7 +16875,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>191</v>
       </c>
@@ -16812,7 +16973,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>193</v>
       </c>
@@ -16910,7 +17071,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>194</v>
       </c>
@@ -17008,7 +17169,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>196</v>
       </c>
@@ -17108,12 +17269,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E3:AE7">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q3:AE3 B3:E7 Q4:S4 W4:X4 AC4:AE4 Q6:AE6 Q7:S7 W7:X7 AC7:AE7 N5:AE5 I3:M7">
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
+  <conditionalFormatting sqref="Q3:AE3 B3:E7 I3:M7 Q4:S4 W4:X4 AC4:AE4 N5:AE5 Q6:AE6 Q7:S7 W7:X7 AC7:AE7">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17124,10 +17285,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA691ACA-93ED-4815-AE98-5327707E2A32}">
-  <dimension ref="A1:AO30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AS31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="54.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>198</v>
       </c>
@@ -17150,109 +17314,118 @@
         <v>200</v>
       </c>
       <c r="H1" t="s">
+        <v>377</v>
+      </c>
+      <c r="I1" t="s">
         <v>201</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>376</v>
+      </c>
+      <c r="K1" t="s">
         <v>202</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>203</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>204</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
+        <v>378</v>
+      </c>
+      <c r="O1" t="s">
         <v>205</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>206</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>186</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>185</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>163</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>164</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>172</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>165</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>166</v>
       </c>
-      <c r="U1" t="s">
+      <c r="X1" t="s">
         <v>207</v>
       </c>
-      <c r="V1" t="s">
+      <c r="Y1" t="s">
         <v>208</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Z1" t="s">
         <v>209</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AA1" t="s">
         <v>210</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AB1" t="s">
         <v>211</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AC1" t="s">
         <v>212</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AD1" t="s">
         <v>213</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AE1" t="s">
         <v>214</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AF1" t="s">
         <v>215</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AG1" t="s">
         <v>216</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AH1" t="s">
         <v>217</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AI1" t="s">
         <v>218</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AJ1" t="s">
         <v>219</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AK1" t="s">
         <v>220</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AL1" t="s">
         <v>221</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AM1" t="s">
         <v>222</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AN1" t="s">
         <v>223</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AO1" t="s">
         <v>224</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AP1" t="s">
         <v>225</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AQ1" t="s">
         <v>226</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AR1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -17274,15 +17447,9 @@
       <c r="G2" t="s">
         <v>356</v>
       </c>
-      <c r="H2" t="s">
-        <v>356</v>
-      </c>
       <c r="I2" t="s">
         <v>356</v>
       </c>
-      <c r="J2" t="s">
-        <v>356</v>
-      </c>
       <c r="K2" t="s">
         <v>356</v>
       </c>
@@ -17292,9 +17459,6 @@
       <c r="M2" t="s">
         <v>356</v>
       </c>
-      <c r="N2" t="s">
-        <v>356</v>
-      </c>
       <c r="O2" t="s">
         <v>356</v>
       </c>
@@ -17376,8 +17540,17 @@
       <c r="AO2" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP2" t="s">
+        <v>356</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>356</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>228</v>
       </c>
@@ -17411,33 +17584,33 @@
       <c r="K3" s="15">
         <v>0</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="15">
+        <v>0</v>
+      </c>
+      <c r="M3" s="15">
+        <v>0</v>
+      </c>
+      <c r="N3" s="15">
+        <v>0</v>
+      </c>
+      <c r="O3" s="8">
         <v>317</v>
       </c>
-      <c r="M3" s="15">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" s="16">
+      <c r="P3" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3" s="16">
         <v>500</v>
       </c>
-      <c r="P3" s="8">
+      <c r="S3" s="8">
         <v>75</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="T3" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
         <v>0</v>
       </c>
@@ -17501,8 +17674,17 @@
       <c r="AO3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>231</v>
       </c>
@@ -17536,33 +17718,33 @@
       <c r="K4" s="15">
         <v>0</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="15">
+        <v>0</v>
+      </c>
+      <c r="M4" s="15">
+        <v>0</v>
+      </c>
+      <c r="N4" s="15">
+        <v>0</v>
+      </c>
+      <c r="O4" s="13">
         <v>1000</v>
       </c>
-      <c r="M4" s="15">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" s="16">
+      <c r="P4" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4" s="16">
         <v>1000</v>
       </c>
-      <c r="P4" s="13">
+      <c r="S4" s="13">
         <v>1000</v>
       </c>
-      <c r="Q4" s="16">
+      <c r="T4" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R4" s="11">
-        <v>0</v>
-      </c>
-      <c r="S4" s="11">
-        <v>0</v>
-      </c>
-      <c r="T4" s="11">
-        <v>0</v>
-      </c>
       <c r="U4" s="11">
         <v>0</v>
       </c>
@@ -17626,8 +17808,17 @@
       <c r="AO4" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP4" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>232</v>
       </c>
@@ -17661,33 +17852,33 @@
       <c r="K5" s="15">
         <v>0</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="15">
+        <v>0</v>
+      </c>
+      <c r="M5" s="15">
+        <v>0</v>
+      </c>
+      <c r="N5" s="15">
+        <v>0</v>
+      </c>
+      <c r="O5" s="8">
         <v>232</v>
       </c>
-      <c r="M5" s="15">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" s="16">
+      <c r="P5" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5" s="16">
         <v>500</v>
       </c>
-      <c r="P5" s="8">
+      <c r="S5" s="8">
         <v>110</v>
       </c>
-      <c r="Q5" s="16">
+      <c r="T5" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
         <v>0</v>
       </c>
@@ -17751,8 +17942,17 @@
       <c r="AO5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>234</v>
       </c>
@@ -17786,33 +17986,33 @@
       <c r="K6" s="15">
         <v>0</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="15">
+        <v>0</v>
+      </c>
+      <c r="M6" s="15">
+        <v>0</v>
+      </c>
+      <c r="N6" s="15">
+        <v>0</v>
+      </c>
+      <c r="O6" s="8">
         <v>264</v>
       </c>
-      <c r="M6" s="15">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" s="16">
+      <c r="P6" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6" s="16">
         <v>500</v>
       </c>
-      <c r="P6" s="8">
+      <c r="S6" s="8">
         <v>13</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="T6" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
         <v>0</v>
       </c>
@@ -17876,8 +18076,17 @@
       <c r="AO6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>235</v>
       </c>
@@ -17911,33 +18120,33 @@
       <c r="K7" s="15">
         <v>0</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="15">
+        <v>0</v>
+      </c>
+      <c r="M7" s="15">
+        <v>0</v>
+      </c>
+      <c r="N7" s="15">
+        <v>0</v>
+      </c>
+      <c r="O7" s="13">
         <v>1000</v>
       </c>
-      <c r="M7" s="15">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" s="16">
+      <c r="P7" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="16">
         <v>1000</v>
       </c>
-      <c r="P7" s="13">
+      <c r="S7" s="13">
         <v>1000</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="T7" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R7" s="11">
-        <v>0</v>
-      </c>
-      <c r="S7" s="11">
-        <v>0</v>
-      </c>
-      <c r="T7" s="11">
-        <v>0</v>
-      </c>
       <c r="U7" s="11">
         <v>0</v>
       </c>
@@ -18001,8 +18210,17 @@
       <c r="AO7" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP7" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>237</v>
       </c>
@@ -18036,33 +18254,33 @@
       <c r="K8" s="15">
         <v>0</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="15">
+        <v>0</v>
+      </c>
+      <c r="M8" s="15">
+        <v>0</v>
+      </c>
+      <c r="N8" s="15">
+        <v>0</v>
+      </c>
+      <c r="O8" s="8">
         <v>232</v>
       </c>
-      <c r="M8" s="15">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" s="16">
+      <c r="P8" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="16">
         <v>500</v>
       </c>
-      <c r="P8" s="8">
+      <c r="S8" s="8">
         <v>110</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="T8" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
         <v>0</v>
       </c>
@@ -18126,8 +18344,17 @@
       <c r="AO8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>238</v>
       </c>
@@ -18161,33 +18388,33 @@
       <c r="K9" s="15">
         <v>0</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="15">
+        <v>0</v>
+      </c>
+      <c r="M9" s="15">
+        <v>0</v>
+      </c>
+      <c r="N9" s="15">
+        <v>0</v>
+      </c>
+      <c r="O9" s="8">
         <v>5</v>
       </c>
-      <c r="M9" s="15">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" s="16">
+      <c r="P9" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="16">
         <v>500</v>
       </c>
-      <c r="P9" s="8">
+      <c r="S9" s="8">
         <v>23</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="T9" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
         <v>0</v>
       </c>
@@ -18251,8 +18478,17 @@
       <c r="AO9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>240</v>
       </c>
@@ -18286,33 +18522,33 @@
       <c r="K10" s="15">
         <v>0</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="15">
+        <v>0</v>
+      </c>
+      <c r="M10" s="15">
+        <v>0</v>
+      </c>
+      <c r="N10" s="15">
+        <v>0</v>
+      </c>
+      <c r="O10" s="13">
         <v>1000</v>
       </c>
-      <c r="M10" s="15">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" s="16">
+      <c r="P10" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10" s="16">
         <v>1000</v>
       </c>
-      <c r="P10" s="13">
+      <c r="S10" s="13">
         <v>1000</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="T10" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R10" s="11">
-        <v>0</v>
-      </c>
-      <c r="S10" s="11">
-        <v>0</v>
-      </c>
-      <c r="T10" s="11">
-        <v>0</v>
-      </c>
       <c r="U10" s="11">
         <v>0</v>
       </c>
@@ -18376,8 +18612,17 @@
       <c r="AO10" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP10" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>241</v>
       </c>
@@ -18411,33 +18656,33 @@
       <c r="K11" s="15">
         <v>0</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="15">
+        <v>0</v>
+      </c>
+      <c r="M11" s="15">
+        <v>0</v>
+      </c>
+      <c r="N11" s="15">
+        <v>0</v>
+      </c>
+      <c r="O11" s="13">
         <v>1000</v>
       </c>
-      <c r="M11" s="15">
-        <v>0</v>
-      </c>
-      <c r="N11" s="11">
-        <v>0</v>
-      </c>
-      <c r="O11" s="16">
+      <c r="P11" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="16">
         <v>1000</v>
       </c>
-      <c r="P11" s="13">
+      <c r="S11" s="13">
         <v>1000</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="T11" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R11" s="11">
-        <v>0</v>
-      </c>
-      <c r="S11" s="11">
-        <v>0</v>
-      </c>
-      <c r="T11" s="11">
-        <v>0</v>
-      </c>
       <c r="U11" s="11">
         <v>0</v>
       </c>
@@ -18501,8 +18746,17 @@
       <c r="AO11" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP11" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>243</v>
       </c>
@@ -18536,33 +18790,33 @@
       <c r="K12" s="15">
         <v>0</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="15">
+        <v>0</v>
+      </c>
+      <c r="M12" s="15">
+        <v>0</v>
+      </c>
+      <c r="N12" s="15">
+        <v>0</v>
+      </c>
+      <c r="O12" s="13">
         <v>1000</v>
       </c>
-      <c r="M12" s="15">
-        <v>0</v>
-      </c>
-      <c r="N12" s="11">
-        <v>0</v>
-      </c>
-      <c r="O12" s="16">
+      <c r="P12" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0</v>
+      </c>
+      <c r="R12" s="16">
         <v>1000</v>
       </c>
-      <c r="P12" s="13">
+      <c r="S12" s="13">
         <v>1000</v>
       </c>
-      <c r="Q12" s="16">
+      <c r="T12" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R12" s="11">
-        <v>0</v>
-      </c>
-      <c r="S12" s="11">
-        <v>0</v>
-      </c>
-      <c r="T12" s="11">
-        <v>0</v>
-      </c>
       <c r="U12" s="11">
         <v>0</v>
       </c>
@@ -18626,8 +18880,17 @@
       <c r="AO12" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>245</v>
       </c>
@@ -18661,33 +18924,33 @@
       <c r="K13" s="15">
         <v>0</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="15">
+        <v>0</v>
+      </c>
+      <c r="M13" s="15">
+        <v>0</v>
+      </c>
+      <c r="N13" s="15">
+        <v>0</v>
+      </c>
+      <c r="O13" s="8">
         <v>26</v>
       </c>
-      <c r="M13" s="15">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" s="16">
+      <c r="P13" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13" s="16">
         <v>500</v>
       </c>
-      <c r="P13" s="8">
+      <c r="S13" s="8">
         <v>38</v>
       </c>
-      <c r="Q13" s="16">
+      <c r="T13" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
         <v>0</v>
       </c>
@@ -18751,8 +19014,17 @@
       <c r="AO13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>246</v>
       </c>
@@ -18786,33 +19058,33 @@
       <c r="K14" s="15">
         <v>0</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="15">
+        <v>0</v>
+      </c>
+      <c r="M14" s="15">
+        <v>0</v>
+      </c>
+      <c r="N14" s="15">
+        <v>0</v>
+      </c>
+      <c r="O14" s="8">
         <v>42</v>
       </c>
-      <c r="M14" s="15">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" s="16">
+      <c r="P14" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14" s="16">
         <v>500</v>
       </c>
-      <c r="P14" s="8">
+      <c r="S14" s="8">
         <v>45</v>
       </c>
-      <c r="Q14" s="16">
+      <c r="T14" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
         <v>0</v>
       </c>
@@ -18876,8 +19148,17 @@
       <c r="AO14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>247</v>
       </c>
@@ -18911,33 +19192,33 @@
       <c r="K15" s="15">
         <v>0</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="15">
+        <v>0</v>
+      </c>
+      <c r="M15" s="15">
+        <v>0</v>
+      </c>
+      <c r="N15" s="15">
+        <v>0</v>
+      </c>
+      <c r="O15" s="13">
         <v>1000</v>
       </c>
-      <c r="M15" s="15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" s="16">
+      <c r="P15" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15" s="16">
         <v>1000</v>
       </c>
-      <c r="P15" s="13">
+      <c r="S15" s="13">
         <v>1000</v>
       </c>
-      <c r="Q15" s="16">
+      <c r="T15" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R15" s="11">
-        <v>0</v>
-      </c>
-      <c r="S15" s="11">
-        <v>0</v>
-      </c>
-      <c r="T15" s="11">
-        <v>0</v>
-      </c>
       <c r="U15" s="11">
         <v>0</v>
       </c>
@@ -19001,8 +19282,17 @@
       <c r="AO15" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>248</v>
       </c>
@@ -19036,33 +19326,33 @@
       <c r="K16" s="15">
         <v>0</v>
       </c>
-      <c r="L16" s="8">
+      <c r="L16" s="15">
+        <v>0</v>
+      </c>
+      <c r="M16" s="15">
+        <v>0</v>
+      </c>
+      <c r="N16" s="15">
+        <v>0</v>
+      </c>
+      <c r="O16" s="8">
         <v>30.1</v>
       </c>
-      <c r="M16" s="15">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" s="16">
+      <c r="P16" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16" s="16">
         <v>500</v>
       </c>
-      <c r="P16" s="8">
+      <c r="S16" s="8">
         <v>37</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="T16" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R16" s="7">
-        <v>0</v>
-      </c>
-      <c r="S16" s="7">
-        <v>0</v>
-      </c>
-      <c r="T16" s="7">
-        <v>0</v>
-      </c>
       <c r="U16" s="7">
         <v>0</v>
       </c>
@@ -19126,8 +19416,17 @@
       <c r="AO16" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP16" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>250</v>
       </c>
@@ -19161,57 +19460,57 @@
       <c r="K17" s="15">
         <v>0</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L17" s="15">
+        <v>0</v>
+      </c>
+      <c r="M17" s="15">
+        <v>0</v>
+      </c>
+      <c r="N17" s="15">
+        <v>0</v>
+      </c>
+      <c r="O17" s="8">
         <v>8</v>
       </c>
-      <c r="M17" s="15">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" s="16">
+      <c r="P17" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17" s="16">
         <v>999</v>
       </c>
-      <c r="P17" s="8">
+      <c r="S17" s="8">
         <v>142</v>
       </c>
-      <c r="Q17" s="16">
+      <c r="T17" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17" s="16" t="s">
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="V17" s="16" t="s">
+      <c r="Y17" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17" s="8">
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="8">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Y17" s="8">
+      <c r="AB17" s="8">
         <v>100</v>
       </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
       <c r="AC17">
         <v>0</v>
       </c>
@@ -19251,8 +19550,17 @@
       <c r="AO17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>255</v>
       </c>
@@ -19286,57 +19594,57 @@
       <c r="K18" s="15">
         <v>0</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="15">
+        <v>0</v>
+      </c>
+      <c r="M18" s="15">
+        <v>0</v>
+      </c>
+      <c r="N18" s="15">
+        <v>0</v>
+      </c>
+      <c r="O18" s="8">
         <v>8</v>
       </c>
-      <c r="M18" s="15">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" s="16">
+      <c r="P18" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18" s="16">
         <v>10000</v>
       </c>
-      <c r="P18" s="8">
+      <c r="S18" s="8">
         <v>40</v>
       </c>
-      <c r="Q18" s="16">
+      <c r="T18" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18" s="16" t="s">
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="V18" s="16" t="s">
+      <c r="Y18" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18" s="8">
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="8">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Y18" s="8">
+      <c r="AB18" s="8">
         <v>100</v>
       </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
       <c r="AC18">
         <v>0</v>
       </c>
@@ -19376,8 +19684,17 @@
       <c r="AO18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>256</v>
       </c>
@@ -19411,63 +19728,63 @@
       <c r="K19" s="15">
         <v>0</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="15">
+        <v>0</v>
+      </c>
+      <c r="M19" s="15">
+        <v>0</v>
+      </c>
+      <c r="N19" s="15">
+        <v>0</v>
+      </c>
+      <c r="O19" s="8">
         <v>12</v>
       </c>
-      <c r="M19" s="15">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" s="16">
+      <c r="P19" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19" s="16">
         <v>500</v>
       </c>
-      <c r="P19" s="8">
+      <c r="S19" s="8">
         <v>137</v>
       </c>
-      <c r="Q19" s="16">
+      <c r="T19" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19" s="16" t="s">
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="V19" s="16" t="s">
+      <c r="Y19" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19" s="8">
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="8">
         <v>0.4</v>
       </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="8">
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="8">
         <v>3</v>
       </c>
-      <c r="AA19" s="8">
+      <c r="AD19" s="8">
         <v>0.8</v>
       </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
       <c r="AE19">
         <v>0</v>
       </c>
@@ -19501,8 +19818,17 @@
       <c r="AO19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>259</v>
       </c>
@@ -19536,63 +19862,63 @@
       <c r="K20" s="15">
         <v>0</v>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="15">
+        <v>0</v>
+      </c>
+      <c r="M20" s="15">
+        <v>0</v>
+      </c>
+      <c r="N20" s="15">
+        <v>0</v>
+      </c>
+      <c r="O20" s="8">
         <v>12</v>
       </c>
-      <c r="M20" s="15">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" s="16">
+      <c r="P20" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20" s="16">
         <v>10000</v>
       </c>
-      <c r="P20" s="8">
+      <c r="S20" s="8">
         <v>59</v>
       </c>
-      <c r="Q20" s="16">
+      <c r="T20" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20" s="16" t="s">
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="V20" s="16" t="s">
+      <c r="Y20" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20" s="8">
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="8">
         <v>0.4</v>
       </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="8">
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="8">
         <v>3</v>
       </c>
-      <c r="AA20" s="8">
+      <c r="AD20" s="8">
         <v>0.8</v>
       </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
       <c r="AE20">
         <v>0</v>
       </c>
@@ -19626,8 +19952,17 @@
       <c r="AO20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>260</v>
       </c>
@@ -19661,54 +19996,54 @@
       <c r="K21" s="15">
         <v>0</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="15">
+        <v>0</v>
+      </c>
+      <c r="M21" s="15">
+        <v>0</v>
+      </c>
+      <c r="N21" s="15">
+        <v>0</v>
+      </c>
+      <c r="O21" s="8">
         <v>9</v>
       </c>
-      <c r="M21" s="15">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" s="16">
+      <c r="P21" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21" s="16">
         <v>10000</v>
       </c>
-      <c r="P21" s="8">
+      <c r="S21" s="8">
         <v>72</v>
       </c>
-      <c r="Q21" s="16">
+      <c r="T21" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21" s="16" t="s">
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="V21" s="16" t="s">
+      <c r="Y21" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21" s="8">
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="8">
         <v>0.5</v>
       </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
       <c r="AB21">
         <v>0</v>
       </c>
@@ -19751,8 +20086,17 @@
       <c r="AO21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>263</v>
       </c>
@@ -19786,54 +20130,54 @@
       <c r="K22" s="15">
         <v>0</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="15">
+        <v>0</v>
+      </c>
+      <c r="M22" s="15">
+        <v>0</v>
+      </c>
+      <c r="N22" s="15">
+        <v>0</v>
+      </c>
+      <c r="O22" s="13">
         <v>1000</v>
       </c>
-      <c r="M22" s="15">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" s="16">
+      <c r="P22" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22" s="16">
         <v>1000</v>
       </c>
-      <c r="P22" s="13">
+      <c r="S22" s="13">
         <v>1000</v>
       </c>
-      <c r="Q22" s="16">
+      <c r="T22" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R22" s="11">
-        <v>0</v>
-      </c>
-      <c r="S22" s="11">
-        <v>0</v>
-      </c>
-      <c r="T22" s="11">
-        <v>0</v>
-      </c>
-      <c r="U22" s="16" t="s">
+      <c r="U22" s="11">
+        <v>0</v>
+      </c>
+      <c r="V22" s="11">
+        <v>0</v>
+      </c>
+      <c r="W22" s="11">
+        <v>0</v>
+      </c>
+      <c r="X22" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="V22" s="16" t="s">
+      <c r="Y22" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="W22" s="11">
-        <v>0</v>
-      </c>
-      <c r="X22" s="8">
+      <c r="Z22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="8">
         <v>0.5</v>
       </c>
-      <c r="Y22" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="11">
-        <v>0</v>
-      </c>
       <c r="AB22" s="11">
         <v>0</v>
       </c>
@@ -19876,8 +20220,17 @@
       <c r="AO22" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR22" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>265</v>
       </c>
@@ -19911,53 +20264,53 @@
       <c r="K23" s="15">
         <v>0</v>
       </c>
-      <c r="L23" s="13">
+      <c r="L23" s="15">
+        <v>0</v>
+      </c>
+      <c r="M23" s="15">
+        <v>0</v>
+      </c>
+      <c r="N23" s="15">
+        <v>0</v>
+      </c>
+      <c r="O23" s="13">
         <v>1000</v>
       </c>
-      <c r="M23" s="15">
-        <v>0</v>
-      </c>
-      <c r="N23" s="11">
-        <v>0</v>
-      </c>
-      <c r="O23" s="16">
+      <c r="P23" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="11">
+        <v>0</v>
+      </c>
+      <c r="R23" s="16">
         <v>10000</v>
       </c>
-      <c r="P23" s="13">
+      <c r="S23" s="13">
         <v>1000</v>
       </c>
-      <c r="Q23" s="16">
+      <c r="T23" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R23" s="11">
-        <v>0</v>
-      </c>
-      <c r="S23" s="11">
-        <v>0</v>
-      </c>
-      <c r="T23" s="11">
-        <v>0</v>
-      </c>
-      <c r="U23" s="16" t="s">
+      <c r="U23" s="11">
+        <v>0</v>
+      </c>
+      <c r="V23" s="11">
+        <v>0</v>
+      </c>
+      <c r="W23" s="11">
+        <v>0</v>
+      </c>
+      <c r="X23" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="V23" s="16" t="s">
+      <c r="Y23" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="W23" s="11">
-        <v>0</v>
-      </c>
-      <c r="X23" s="8">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="11">
-        <v>0</v>
-      </c>
       <c r="Z23" s="11">
         <v>0</v>
       </c>
-      <c r="AA23" s="11">
-        <v>0</v>
+      <c r="AA23" s="8">
+        <v>1</v>
       </c>
       <c r="AB23" s="11">
         <v>0</v>
@@ -20001,8 +20354,17 @@
       <c r="AO23" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR23" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>268</v>
       </c>
@@ -20036,33 +20398,33 @@
       <c r="K24" s="15">
         <v>0</v>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="15">
+        <v>0</v>
+      </c>
+      <c r="M24" s="15">
+        <v>0</v>
+      </c>
+      <c r="N24" s="15">
+        <v>0</v>
+      </c>
+      <c r="O24" s="8">
         <v>347</v>
       </c>
-      <c r="M24" s="8">
+      <c r="P24" s="8">
         <v>225</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24" s="16">
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24" s="16">
         <v>10000</v>
       </c>
-      <c r="P24" s="8">
+      <c r="S24" s="8">
         <v>129</v>
       </c>
-      <c r="Q24" s="16">
+      <c r="T24" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
       <c r="U24">
         <v>0</v>
       </c>
@@ -20126,8 +20488,17 @@
       <c r="AO24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>270</v>
       </c>
@@ -20161,33 +20532,33 @@
       <c r="K25" s="15">
         <v>0</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="15">
+        <v>0</v>
+      </c>
+      <c r="M25" s="15">
+        <v>0</v>
+      </c>
+      <c r="N25" s="15">
+        <v>0</v>
+      </c>
+      <c r="O25" s="8">
         <v>140</v>
       </c>
-      <c r="M25" s="8">
+      <c r="P25" s="8">
         <v>97</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" s="16">
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25" s="16">
         <v>10000</v>
       </c>
-      <c r="P25" s="8">
+      <c r="S25" s="8">
         <v>130</v>
       </c>
-      <c r="Q25" s="16">
+      <c r="T25" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
       <c r="U25">
         <v>0</v>
       </c>
@@ -20251,8 +20622,17 @@
       <c r="AO25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>272</v>
       </c>
@@ -20286,33 +20666,33 @@
       <c r="K26" s="15">
         <v>0</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="15">
+        <v>0</v>
+      </c>
+      <c r="M26" s="15">
+        <v>0</v>
+      </c>
+      <c r="N26" s="15">
+        <v>0</v>
+      </c>
+      <c r="O26" s="8">
         <v>95</v>
       </c>
-      <c r="M26" s="8">
+      <c r="P26" s="8">
         <v>55</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" s="16">
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26" s="16">
         <v>10000</v>
       </c>
-      <c r="P26" s="8">
+      <c r="S26" s="8">
         <v>765</v>
       </c>
-      <c r="Q26" s="16">
+      <c r="T26" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
       <c r="U26">
         <v>0</v>
       </c>
@@ -20376,8 +20756,17 @@
       <c r="AO26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>274</v>
       </c>
@@ -20411,33 +20800,33 @@
       <c r="K27" s="15">
         <v>0</v>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="15">
+        <v>0</v>
+      </c>
+      <c r="M27" s="15">
+        <v>0</v>
+      </c>
+      <c r="N27" s="15">
+        <v>0</v>
+      </c>
+      <c r="O27" s="8">
         <v>95</v>
       </c>
-      <c r="M27" s="8">
+      <c r="P27" s="8">
         <v>55</v>
       </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" s="16">
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27" s="16">
         <v>10000</v>
       </c>
-      <c r="P27" s="8">
+      <c r="S27" s="8">
         <v>765</v>
       </c>
-      <c r="Q27" s="16">
+      <c r="T27" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
       <c r="U27">
         <v>0</v>
       </c>
@@ -20501,8 +20890,17 @@
       <c r="AO27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP27">
+        <v>0</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>276</v>
       </c>
@@ -20534,33 +20932,33 @@
       <c r="K28" s="15">
         <v>0</v>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="15">
+        <v>0</v>
+      </c>
+      <c r="M28" s="15">
+        <v>0</v>
+      </c>
+      <c r="N28" s="15">
+        <v>0</v>
+      </c>
+      <c r="O28" s="8">
         <v>1.3</v>
       </c>
-      <c r="M28" s="15">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28" s="16">
+      <c r="P28" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28" s="16">
         <v>10000</v>
       </c>
-      <c r="P28" s="8">
+      <c r="S28" s="8">
         <v>77</v>
       </c>
-      <c r="Q28" s="16">
+      <c r="T28" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
       <c r="U28">
         <v>0</v>
       </c>
@@ -20624,8 +21022,17 @@
       <c r="AO28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>277</v>
       </c>
@@ -20657,33 +21064,33 @@
       <c r="K29" s="15">
         <v>0</v>
       </c>
-      <c r="L29" s="8">
+      <c r="L29" s="15">
+        <v>0</v>
+      </c>
+      <c r="M29" s="15">
+        <v>0</v>
+      </c>
+      <c r="N29" s="15">
+        <v>0</v>
+      </c>
+      <c r="O29" s="8">
         <v>10</v>
       </c>
-      <c r="M29" s="15">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29" s="16">
+      <c r="P29" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29" s="16">
         <v>10000</v>
       </c>
-      <c r="P29" s="8">
+      <c r="S29" s="8">
         <v>67</v>
       </c>
-      <c r="Q29" s="16">
+      <c r="T29" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
       <c r="U29">
         <v>0</v>
       </c>
@@ -20747,8 +21154,17 @@
       <c r="AO29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>278</v>
       </c>
@@ -20782,33 +21198,33 @@
       <c r="K30" s="15">
         <v>0</v>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="15">
+        <v>0</v>
+      </c>
+      <c r="M30" s="15">
+        <v>0</v>
+      </c>
+      <c r="N30" s="15">
+        <v>0</v>
+      </c>
+      <c r="O30" s="8">
         <v>10</v>
       </c>
-      <c r="M30" s="13">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30" s="16">
+      <c r="P30" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30" s="16">
         <v>10000</v>
       </c>
-      <c r="P30" s="8">
+      <c r="S30" s="8">
         <v>480</v>
       </c>
-      <c r="Q30" s="16">
+      <c r="T30" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
       <c r="U30">
         <v>0</v>
       </c>
@@ -20870,62 +21286,233 @@
         <v>0</v>
       </c>
       <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>0</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="A31" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="B31" s="25">
+        <v>1</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="F31" s="25">
+        <v>3.5</v>
+      </c>
+      <c r="G31" s="25">
+        <v>0.375</v>
+      </c>
+      <c r="H31" s="25">
+        <v>0.8</v>
+      </c>
+      <c r="I31" s="25">
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="J31" s="15">
+        <v>0</v>
+      </c>
+      <c r="K31" s="25">
+        <v>0</v>
+      </c>
+      <c r="L31" s="25">
+        <v>0</v>
+      </c>
+      <c r="M31" s="15">
+        <v>0</v>
+      </c>
+      <c r="N31" s="15">
+        <v>0</v>
+      </c>
+      <c r="O31" s="25">
+        <v>0</v>
+      </c>
+      <c r="P31" s="25">
+        <v>347</v>
+      </c>
+      <c r="Q31" s="25">
+        <v>225</v>
+      </c>
+      <c r="R31" s="25">
+        <v>0</v>
+      </c>
+      <c r="S31" s="25">
+        <v>10000</v>
+      </c>
+      <c r="T31" s="25">
+        <v>129</v>
+      </c>
+      <c r="U31" s="25">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="V31" s="25">
+        <v>0</v>
+      </c>
+      <c r="W31" s="25">
+        <v>0</v>
+      </c>
+      <c r="X31" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="25">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AR31" s="25">
+        <v>0</v>
+      </c>
+      <c r="AS31" s="25">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B23:E30">
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="11" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:AO30">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+  <conditionalFormatting sqref="K10:L30 J10:J31 F3:AR3 F4:G30 O4:AR30 M4:N31 I4:L9 I10:I30 H4:H31">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N30">
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+  <conditionalFormatting sqref="Q4:Q30">
+    <cfRule type="cellIs" dxfId="13" priority="16" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:O3">
-    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
+  <conditionalFormatting sqref="Q3:R3">
+    <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O8:O9 B8:E9">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+  <conditionalFormatting sqref="R8:R9 B8:E9">
+    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O13:O14 R13:W21 AB13:AO21 O16:O21 B13:E21">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+  <conditionalFormatting sqref="R13:R14 U13:Z21 AE13:AR21 R16:R21 B13:E21">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O23:O30 R23:W30 AB23:AO30">
+  <conditionalFormatting sqref="R23:R30 U23:Z30 AE23:AR30">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U3:AR6 R5:R6 U8:AR9 AA13:AD16 AB19:AB21 AC21:AD21 AB23 AA24:AD30 B3:E6">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC17:AD18">
+    <cfRule type="cellIs" dxfId="7" priority="13" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:E31">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31:G31 K31:L31 O31:AS31 I31">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R31">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:AO6 O5:O6 R8:AO9 X13:AA16 Y19:Y21 Z21:AA21 Y23 X24:AA30 B3:E6">
+  <conditionalFormatting sqref="S31 V31:AA31 AF31:AS31">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z17:AA18">
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
+  <conditionalFormatting sqref="AB31:AE31">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20936,12 +21523,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{062F9C9F-EC6B-45A0-B400-3E864B701D31}">
   <dimension ref="A1:AA8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>280</v>
       </c>
@@ -21024,7 +21611,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -21107,7 +21694,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>292</v>
       </c>
@@ -21190,7 +21777,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>294</v>
       </c>
@@ -21273,7 +21860,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>295</v>
       </c>
@@ -21356,7 +21943,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>296</v>
       </c>
@@ -21439,7 +22026,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>297</v>
       </c>
@@ -21522,7 +22109,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>298</v>
       </c>
@@ -21612,13 +22199,13 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F7A117-64AB-4955-A232-50A2E399D809}">
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="58.453125" customWidth="1"/>
+    <col min="1" max="1" width="58.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>299</v>
       </c>
@@ -21665,7 +22252,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -21712,7 +22299,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>302</v>
       </c>
@@ -21759,7 +22346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>304</v>
       </c>
@@ -21806,7 +22393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>305</v>
       </c>
@@ -21853,7 +22440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>306</v>
       </c>
@@ -21900,7 +22487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>307</v>
       </c>
@@ -21947,7 +22534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>308</v>
       </c>
@@ -21994,7 +22581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>309</v>
       </c>
@@ -22041,7 +22628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>310</v>
       </c>
@@ -22088,7 +22675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>311</v>
       </c>
@@ -22135,7 +22722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>312</v>
       </c>
@@ -22182,7 +22769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>313</v>
       </c>
@@ -22229,7 +22816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>314</v>
       </c>
@@ -22276,7 +22863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>315</v>
       </c>
@@ -22323,7 +22910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>316</v>
       </c>
@@ -22370,7 +22957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>317</v>
       </c>
@@ -22417,7 +23004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>318</v>
       </c>
@@ -22464,7 +23051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>319</v>
       </c>
@@ -22511,7 +23098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>320</v>
       </c>
@@ -22558,7 +23145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>321</v>
       </c>
@@ -22602,6 +23189,53 @@
         <v>0</v>
       </c>
       <c r="O21" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="B22" s="25">
+        <v>1</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="D22" s="25">
+        <v>1</v>
+      </c>
+      <c r="E22" s="25">
+        <v>0</v>
+      </c>
+      <c r="F22" s="25">
+        <v>0</v>
+      </c>
+      <c r="G22" s="25">
+        <v>0</v>
+      </c>
+      <c r="H22" s="25">
+        <v>9999</v>
+      </c>
+      <c r="I22" s="25">
+        <v>0</v>
+      </c>
+      <c r="J22" s="25">
+        <v>0</v>
+      </c>
+      <c r="K22" s="25">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="L22" s="25">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M22" s="25">
+        <v>0</v>
+      </c>
+      <c r="N22" s="25">
+        <v>0</v>
+      </c>
+      <c r="O22" s="25">
         <v>0</v>
       </c>
     </row>

--- a/template_examples/standard_parameters_example.xlsx
+++ b/template_examples/standard_parameters_example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FranziskaKoert\Documents\Github\SESMG-dev-20260709\template_examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1A14DF-44DA-48BD-9391-3326DA05DCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5675DE-F42C-44AA-95E8-112671D44EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="6" xr2:uid="{D48BE4BC-BA48-4DC0-B3DF-D04B8CFD99C7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="5" activeTab="6" xr2:uid="{D48BE4BC-BA48-4DC0-B3DF-D04B8CFD99C7}"/>
   </bookViews>
   <sheets>
     <sheet name="energysystem" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="378">
   <si>
     <t>start date</t>
   </si>
@@ -595,9 +595,6 @@
   </si>
   <si>
     <t>peripheral losses</t>
-  </si>
-  <si>
-    <t>electric consumption</t>
   </si>
   <si>
     <t>cleanliness</t>
@@ -1241,7 +1238,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1318,12 +1315,6 @@
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor rgb="FFDAE3F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1425,17 +1416,381 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 3" xfId="1" xr:uid="{3EB3DAA0-9F71-48CB-8FEA-1E1CAF40E04C}"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="80">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1985,34 +2340,34 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2065,27 +2420,27 @@
         <v>117</v>
       </c>
       <c r="B1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C1" t="s">
         <v>322</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>323</v>
-      </c>
-      <c r="D1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -3602,7 +3957,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B111" s="8">
         <v>0.35</v>
@@ -3616,7 +3971,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B112" s="8">
         <v>0.21</v>
@@ -3644,7 +3999,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B114" s="8">
         <v>7.14</v>
@@ -3672,7 +4027,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B116" s="8">
         <v>286</v>
@@ -3686,12 +4041,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C112:D112 C114:D114 C116:D116 A3:A116">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C112:D116">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3717,25 +4072,25 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>332</v>
-      </c>
       <c r="F1" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>163</v>
@@ -3750,68 +4105,68 @@
         <v>166</v>
       </c>
       <c r="L1" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>335</v>
-      </c>
       <c r="O1" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B3" s="18">
         <v>0</v>
@@ -3844,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M3" s="18">
         <v>1</v>
@@ -3858,7 +4213,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B4" s="18">
         <v>0</v>
@@ -3891,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M4" s="18">
         <v>1</v>
@@ -3905,7 +4260,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B5" s="18">
         <v>0</v>
@@ -3938,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M5" s="18">
         <v>1</v>
@@ -3952,7 +4307,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B6" s="18">
         <v>0</v>
@@ -3985,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M6" s="18">
         <v>1</v>
@@ -3999,7 +4354,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B7" s="18">
         <v>0</v>
@@ -4032,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M7" s="18">
         <v>1</v>
@@ -4046,7 +4401,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B8" s="18">
         <v>0</v>
@@ -4079,7 +4434,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M8" s="18">
         <v>0</v>
@@ -4093,7 +4448,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B9" s="18">
         <v>0</v>
@@ -4126,7 +4481,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M9" s="18">
         <v>1</v>
@@ -4140,7 +4495,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B10" s="18">
         <v>0</v>
@@ -4173,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M10" s="18">
         <v>1</v>
@@ -4187,7 +4542,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B11" s="18">
         <v>0</v>
@@ -4220,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M11" s="18">
         <v>1</v>
@@ -4234,7 +4589,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B12" s="18">
         <v>0</v>
@@ -4267,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M12" s="18">
         <v>1</v>
@@ -4281,7 +4636,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B13" s="18">
         <v>0</v>
@@ -4314,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M13" s="18">
         <v>1</v>
@@ -4328,7 +4683,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B14" s="18">
         <v>0</v>
@@ -4361,7 +4716,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M14" s="18">
         <v>1</v>
@@ -4375,7 +4730,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B15" s="18">
         <v>0</v>
@@ -4408,7 +4763,7 @@
         <v>22.28</v>
       </c>
       <c r="L15" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M15" s="18">
         <v>1</v>
@@ -4422,7 +4777,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B16" s="18">
         <v>0</v>
@@ -4455,7 +4810,7 @@
         <v>34.11</v>
       </c>
       <c r="L16" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M16" s="18">
         <v>1</v>
@@ -4469,7 +4824,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B17" s="18">
         <v>0</v>
@@ -4502,7 +4857,7 @@
         <v>46.49</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M17" s="18">
         <v>1</v>
@@ -4516,7 +4871,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B18" s="18">
         <v>0</v>
@@ -4549,7 +4904,7 @@
         <v>65.88</v>
       </c>
       <c r="L18" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M18" s="18">
         <v>1</v>
@@ -4563,7 +4918,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B19" s="18">
         <v>0</v>
@@ -4596,7 +4951,7 @@
         <v>96.2</v>
       </c>
       <c r="L19" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M19" s="18">
         <v>1</v>
@@ -4610,7 +4965,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B20" s="18">
         <v>0</v>
@@ -4643,7 +4998,7 @@
         <v>125.53</v>
       </c>
       <c r="L20" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M20" s="18">
         <v>0</v>
@@ -4657,7 +5012,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B21" s="18">
         <v>0</v>
@@ -4690,7 +5045,7 @@
         <v>156.03</v>
       </c>
       <c r="L21" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M21" s="18">
         <v>1</v>
@@ -4704,7 +5059,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B22" s="18">
         <v>0</v>
@@ -4737,7 +5092,7 @@
         <v>204.8</v>
       </c>
       <c r="L22" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M22" s="18">
         <v>1</v>
@@ -4751,7 +5106,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B23" s="18">
         <v>0</v>
@@ -4784,7 +5139,7 @@
         <v>266.76</v>
       </c>
       <c r="L23" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M23" s="18">
         <v>1</v>
@@ -4798,7 +5153,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B24" s="18">
         <v>0</v>
@@ -4831,7 +5186,7 @@
         <v>323.8</v>
       </c>
       <c r="L24" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M24" s="18">
         <v>1</v>
@@ -4845,7 +5200,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B25" s="18">
         <v>0</v>
@@ -4878,7 +5233,7 @@
         <v>403.26</v>
       </c>
       <c r="L25" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M25" s="18">
         <v>1</v>
@@ -4892,7 +5247,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B26" s="18">
         <v>0</v>
@@ -4925,7 +5280,7 @@
         <v>488.02</v>
       </c>
       <c r="L26" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M26" s="18">
         <v>1</v>
@@ -4939,7 +5294,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B27" s="18">
         <v>0</v>
@@ -4972,7 +5327,7 @@
         <v>605.46</v>
       </c>
       <c r="L27" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M27" s="18">
         <v>1</v>
@@ -4986,7 +5341,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B28" s="18">
         <v>0</v>
@@ -5019,7 +5374,7 @@
         <v>755.61</v>
       </c>
       <c r="L28" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M28" s="18">
         <v>1</v>
@@ -5033,7 +5388,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B29" s="18">
         <v>0</v>
@@ -5066,7 +5421,7 @@
         <v>948.97</v>
       </c>
       <c r="L29" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M29" s="18">
         <v>1</v>
@@ -5080,7 +5435,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B30" s="18">
         <v>0</v>
@@ -5111,7 +5466,7 @@
         <v>1190.8499999999999</v>
       </c>
       <c r="L30" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M30" s="18">
         <v>1</v>
@@ -5125,7 +5480,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B31" s="16">
         <v>1</v>
@@ -5172,7 +5527,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B32" s="16">
         <v>1</v>
@@ -5263,31 +5618,31 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -5638,88 +5993,88 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="16">
-        <v>1</v>
-      </c>
-      <c r="C15" s="16">
-        <v>1</v>
-      </c>
-      <c r="D15" s="16">
-        <v>0</v>
-      </c>
-      <c r="E15" s="8">
+    <row r="15" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="B15" s="25">
+        <v>1</v>
+      </c>
+      <c r="C15" s="25">
+        <v>0</v>
+      </c>
+      <c r="D15" s="25">
+        <v>1</v>
+      </c>
+      <c r="E15" s="25">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0.15620000000000001</v>
+      </c>
+      <c r="G15" s="25">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>44</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="B16" s="25">
+        <v>1</v>
+      </c>
+      <c r="C16" s="25">
+        <v>1</v>
+      </c>
+      <c r="D16" s="25">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8">
         <v>-6.8199999999999997E-2</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" s="8">
-        <v>-347</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="16">
-        <v>1</v>
-      </c>
-      <c r="C16" s="16">
-        <v>1</v>
-      </c>
-      <c r="D16" s="16">
-        <v>0</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.128</v>
-      </c>
-      <c r="F16">
+      <c r="F16" s="25">
         <v>0</v>
       </c>
       <c r="G16" s="8">
         <v>-140</v>
       </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="H16" s="25">
+        <v>0</v>
+      </c>
+      <c r="I16" s="25" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" s="16">
         <v>1</v>
       </c>
       <c r="C17" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="16">
-        <v>1</v>
-      </c>
-      <c r="E17" s="16">
-        <v>0</v>
-      </c>
-      <c r="F17" s="8">
-        <v>0.1958</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8">
-        <v>366</v>
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-6.8199999999999997E-2</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>-347</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
       </c>
       <c r="I17" t="s">
         <v>24</v>
@@ -5727,28 +6082,28 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B18" s="16">
         <v>1</v>
       </c>
       <c r="C18" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="16">
-        <v>1</v>
-      </c>
-      <c r="E18" s="16">
-        <v>0</v>
-      </c>
-      <c r="F18" s="8">
-        <v>0.1958</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18" s="8">
-        <v>366</v>
+        <v>0</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.128</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8">
+        <v>-140</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
       </c>
       <c r="I18" t="s">
         <v>24</v>
@@ -5756,7 +6111,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B19" s="16">
         <v>1</v>
@@ -5765,19 +6120,19 @@
         <v>0</v>
       </c>
       <c r="D19" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="16">
         <v>0</v>
       </c>
-      <c r="F19">
-        <v>0</v>
+      <c r="F19" s="8">
+        <v>0.1958</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
-      <c r="H19">
-        <v>0</v>
+      <c r="H19" s="8">
+        <v>366</v>
       </c>
       <c r="I19" t="s">
         <v>24</v>
@@ -5785,7 +6140,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B20" s="16">
         <v>1</v>
@@ -5794,33 +6149,33 @@
         <v>0</v>
       </c>
       <c r="D20" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="16">
         <v>0</v>
       </c>
-      <c r="F20">
-        <v>0</v>
+      <c r="F20" s="8">
+        <v>0.1958</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
-      <c r="H20">
-        <v>0</v>
+      <c r="H20" s="8">
+        <v>366</v>
       </c>
       <c r="I20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B21" s="16">
         <v>1</v>
       </c>
       <c r="C21" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="16">
         <v>0</v>
@@ -5838,12 +6193,12 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B22" s="16">
         <v>1</v>
@@ -5852,27 +6207,27 @@
         <v>0</v>
       </c>
       <c r="D22" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="16">
         <v>0</v>
       </c>
-      <c r="F22" s="8">
-        <v>0.15620000000000001</v>
+      <c r="F22">
+        <v>0</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
-      <c r="H22" s="8">
-        <v>44</v>
+      <c r="H22">
+        <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B23" s="16">
         <v>1</v>
@@ -5901,7 +6256,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B24" s="16">
         <v>1</v>
@@ -5916,36 +6271,36 @@
         <v>0</v>
       </c>
       <c r="F24" s="8">
-        <v>0.1958</v>
+        <v>0.15620000000000001</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24" s="8">
-        <v>366</v>
+        <v>44</v>
       </c>
       <c r="I24" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B25" s="16">
         <v>1</v>
       </c>
       <c r="C25" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="16">
         <v>0</v>
       </c>
-      <c r="F25" s="8">
-        <v>4.4999999999999998E-2</v>
+      <c r="F25">
+        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5954,33 +6309,33 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B26" s="16">
         <v>1</v>
       </c>
       <c r="C26" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="16">
-        <v>0</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-5.1459999999999999E-2</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26" s="8">
-        <v>-27</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E26" s="16">
+        <v>0</v>
+      </c>
+      <c r="F26" s="8">
+        <v>0.1958</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" s="8">
+        <v>366</v>
       </c>
       <c r="I26" t="s">
         <v>24</v>
@@ -5988,7 +6343,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B27" s="16">
         <v>1</v>
@@ -6003,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="8">
-        <v>9.4500000000000001E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -6017,7 +6372,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B28" s="16">
         <v>1</v>
@@ -6029,13 +6384,13 @@
         <v>0</v>
       </c>
       <c r="E28" s="8">
-        <v>-0.128</v>
+        <v>-5.1459999999999999E-2</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>-95</v>
+        <v>-27</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -6046,7 +6401,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B29" s="16">
         <v>1</v>
@@ -6061,7 +6416,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="8">
-        <v>2.9000000000000001E-2</v>
+        <v>9.4500000000000001E-2</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6075,7 +6430,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B30" s="16">
         <v>1</v>
@@ -6104,7 +6459,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B31" s="16">
         <v>1</v>
@@ -6113,13 +6468,13 @@
         <v>0</v>
       </c>
       <c r="D31" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="16">
         <v>0</v>
       </c>
       <c r="F31" s="8">
-        <v>0</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -6133,36 +6488,36 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B32" s="16">
         <v>1</v>
       </c>
       <c r="C32" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" s="16">
-        <v>1</v>
-      </c>
-      <c r="E32" s="16">
-        <v>0</v>
-      </c>
-      <c r="F32" s="8">
-        <v>9.7000000000000003E-2</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.128</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" s="8">
+        <v>-95</v>
       </c>
       <c r="H32">
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B33" s="16">
         <v>1</v>
@@ -6171,13 +6526,13 @@
         <v>0</v>
       </c>
       <c r="D33" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="16">
         <v>0</v>
       </c>
       <c r="F33" s="8">
-        <v>9.4500000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -6191,7 +6546,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B34" s="16">
         <v>1</v>
@@ -6206,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="8">
-        <v>2.9000000000000001E-2</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -6220,7 +6575,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B35" s="16">
         <v>1</v>
@@ -6234,8 +6589,8 @@
       <c r="E35" s="16">
         <v>0</v>
       </c>
-      <c r="F35" s="13">
-        <v>1000</v>
+      <c r="F35" s="8">
+        <v>9.4500000000000001E-2</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -6248,208 +6603,208 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36">
+      <c r="A36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="16">
+        <v>1</v>
+      </c>
+      <c r="C36" s="16">
+        <v>0</v>
+      </c>
+      <c r="D36" s="16">
+        <v>1</v>
+      </c>
+      <c r="E36" s="16">
         <v>0</v>
       </c>
       <c r="F36" s="8">
-        <v>1.958E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
-      <c r="H36" s="8">
-        <v>366</v>
+      <c r="H36">
+        <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37" s="13">
+      <c r="A37" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="16">
+        <v>1</v>
+      </c>
+      <c r="C37" s="16">
+        <v>0</v>
+      </c>
+      <c r="D37" s="16">
+        <v>1</v>
+      </c>
+      <c r="E37" s="16">
+        <v>0</v>
+      </c>
+      <c r="F37" s="13">
         <v>1000</v>
       </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37" s="13">
-        <v>1000</v>
+      <c r="G37">
+        <v>0</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38" s="8">
+        <v>1.958E-2</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" s="8">
+        <v>366</v>
+      </c>
+      <c r="I38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39" s="13">
+        <v>1000</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-      <c r="I38" t="s">
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="16">
-        <v>1</v>
-      </c>
-      <c r="C39" s="16">
-        <v>0</v>
-      </c>
-      <c r="D39" s="16">
-        <v>1</v>
-      </c>
-      <c r="E39" s="16">
-        <v>0</v>
-      </c>
-      <c r="F39" s="8">
+      <c r="B41" s="16">
+        <v>1</v>
+      </c>
+      <c r="C41" s="16">
+        <v>0</v>
+      </c>
+      <c r="D41" s="16">
+        <v>1</v>
+      </c>
+      <c r="E41" s="16">
+        <v>0</v>
+      </c>
+      <c r="F41" s="8">
         <v>9.4500000000000001E-2</v>
       </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39" t="s">
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="25" t="s">
-        <v>370</v>
-      </c>
-      <c r="B40" s="25">
-        <v>1</v>
-      </c>
-      <c r="C40" s="25">
-        <v>0</v>
-      </c>
-      <c r="D40" s="25">
-        <v>1</v>
-      </c>
-      <c r="E40" s="25">
-        <v>0</v>
-      </c>
-      <c r="F40" s="25">
-        <v>0.15620000000000001</v>
-      </c>
-      <c r="G40" s="25">
-        <v>0</v>
-      </c>
-      <c r="H40" s="25">
-        <v>44</v>
-      </c>
-      <c r="I40" s="25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="25" t="s">
-        <v>371</v>
-      </c>
-      <c r="B41" s="25">
-        <v>1</v>
-      </c>
-      <c r="C41" s="25">
-        <v>1</v>
-      </c>
-      <c r="D41" s="25">
-        <v>0</v>
-      </c>
-      <c r="E41" s="25">
-        <v>-6.8199999999999997E-2</v>
-      </c>
-      <c r="F41" s="25">
-        <v>0</v>
-      </c>
-      <c r="G41" s="25">
-        <v>-140</v>
-      </c>
-      <c r="H41" s="25">
-        <v>0</v>
-      </c>
-      <c r="I41" s="25" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B3:B22 B24:B35">
-    <cfRule type="cellIs" dxfId="27" priority="7" operator="equal">
+  <conditionalFormatting sqref="B3:B24 B26:B37">
+    <cfRule type="cellIs" dxfId="79" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B39">
-    <cfRule type="cellIs" dxfId="26" priority="6" operator="equal">
+  <conditionalFormatting sqref="B41">
+    <cfRule type="cellIs" dxfId="78" priority="6" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:H39">
-    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
+  <conditionalFormatting sqref="B3:H41">
+    <cfRule type="cellIs" dxfId="77" priority="4" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B40:B41">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
+  <conditionalFormatting sqref="B15:B16">
+    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B40:H41">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+  <conditionalFormatting sqref="B15:H16">
+    <cfRule type="cellIs" dxfId="74" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6501,34 +6856,34 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -7619,7 +7974,7 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" t="s">
         <v>143</v>
@@ -16339,7 +16694,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3:A110">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16425,7 +16780,7 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" t="s">
         <v>156</v>
@@ -16572,16 +16927,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865B2AF4-2CF4-4093-8D70-C931333F20A4}">
-  <dimension ref="A1:AF7"/>
+  <dimension ref="A1:AE7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.44140625" customWidth="1"/>
     <col min="25" max="25" width="20.6640625" customWidth="1"/>
-    <col min="32" max="32" width="15" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>159</v>
       </c>
@@ -16619,7 +16974,7 @@
         <v>168</v>
       </c>
       <c r="M1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N1" t="s">
         <v>169</v>
@@ -16673,122 +17028,116 @@
         <v>185</v>
       </c>
       <c r="AE1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F2" t="s">
+        <v>355</v>
+      </c>
+      <c r="G2" t="s">
+        <v>355</v>
+      </c>
+      <c r="H2" t="s">
+        <v>355</v>
+      </c>
+      <c r="I2" t="s">
+        <v>355</v>
+      </c>
+      <c r="J2" t="s">
+        <v>355</v>
+      </c>
+      <c r="K2" t="s">
+        <v>355</v>
+      </c>
+      <c r="L2" t="s">
+        <v>355</v>
+      </c>
+      <c r="M2" t="s">
+        <v>355</v>
+      </c>
+      <c r="N2" t="s">
+        <v>355</v>
+      </c>
+      <c r="O2" t="s">
+        <v>355</v>
+      </c>
+      <c r="P2" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>355</v>
+      </c>
+      <c r="R2" t="s">
+        <v>355</v>
+      </c>
+      <c r="S2" t="s">
+        <v>355</v>
+      </c>
+      <c r="T2" t="s">
+        <v>355</v>
+      </c>
+      <c r="U2" t="s">
+        <v>355</v>
+      </c>
+      <c r="V2" t="s">
+        <v>355</v>
+      </c>
+      <c r="W2" t="s">
+        <v>355</v>
+      </c>
+      <c r="X2" t="s">
+        <v>355</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>355</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>355</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>355</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>355</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>355</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>355</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>186</v>
       </c>
-      <c r="AF1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>356</v>
-      </c>
-      <c r="B2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D2" t="s">
-        <v>356</v>
-      </c>
-      <c r="E2" t="s">
-        <v>356</v>
-      </c>
-      <c r="F2" t="s">
-        <v>356</v>
-      </c>
-      <c r="G2" t="s">
-        <v>356</v>
-      </c>
-      <c r="H2" t="s">
-        <v>356</v>
-      </c>
-      <c r="I2" t="s">
-        <v>356</v>
-      </c>
-      <c r="J2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K2" t="s">
-        <v>356</v>
-      </c>
-      <c r="L2" t="s">
-        <v>356</v>
-      </c>
-      <c r="M2" t="s">
-        <v>356</v>
-      </c>
-      <c r="N2" t="s">
-        <v>356</v>
-      </c>
-      <c r="O2" t="s">
-        <v>356</v>
-      </c>
-      <c r="P2" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>356</v>
-      </c>
-      <c r="R2" t="s">
-        <v>356</v>
-      </c>
-      <c r="S2" t="s">
-        <v>356</v>
-      </c>
-      <c r="T2" t="s">
-        <v>356</v>
-      </c>
-      <c r="U2" t="s">
-        <v>356</v>
-      </c>
-      <c r="V2" t="s">
-        <v>356</v>
-      </c>
-      <c r="W2" t="s">
-        <v>356</v>
-      </c>
-      <c r="X2" t="s">
-        <v>356</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>356</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>356</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>356</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>356</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>356</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>356</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>356</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" s="16">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16">
+        <v>1</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>187</v>
-      </c>
-      <c r="B3" s="16">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16">
-        <v>1</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>188</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -16809,10 +17158,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="L3" s="16" t="s">
         <v>189</v>
-      </c>
-      <c r="L3" s="16" t="s">
-        <v>190</v>
       </c>
       <c r="M3" s="16">
         <v>1</v>
@@ -16868,25 +17217,22 @@
       <c r="AD3">
         <v>0</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="16" t="s">
+      <c r="AE3" s="16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" s="16">
+        <v>1</v>
+      </c>
+      <c r="C4" s="16">
+        <v>1</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>191</v>
-      </c>
-      <c r="B4" s="16">
-        <v>1</v>
-      </c>
-      <c r="C4" s="16">
-        <v>1</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>192</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -16957,8 +17303,8 @@
       <c r="AA4" s="8">
         <v>0.09</v>
       </c>
-      <c r="AB4" s="8">
-        <v>0.02</v>
+      <c r="AB4">
+        <v>0</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -16966,16 +17312,13 @@
       <c r="AD4">
         <v>0</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="16" t="s">
+      <c r="AE4" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B5" s="16">
         <v>1</v>
@@ -17059,21 +17402,18 @@
         <v>0</v>
       </c>
       <c r="AC5" s="16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AD5" s="16">
-        <v>20</v>
-      </c>
-      <c r="AE5" s="16">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B6" s="16">
         <v>1</v>
@@ -17082,7 +17422,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -17103,10 +17443,10 @@
         <v>0</v>
       </c>
       <c r="K6" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="L6" s="16" t="s">
         <v>189</v>
-      </c>
-      <c r="L6" s="16" t="s">
-        <v>190</v>
       </c>
       <c r="M6" s="16">
         <v>1</v>
@@ -17162,17 +17502,14 @@
       <c r="AD6">
         <v>0</v>
       </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="16" t="s">
+      <c r="AE6" s="16" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>196</v>
-      </c>
       <c r="B7" s="16">
         <v>1</v>
       </c>
@@ -17180,7 +17517,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -17251,8 +17588,8 @@
       <c r="AA7" s="8">
         <v>0.09</v>
       </c>
-      <c r="AB7" s="8">
-        <v>0.02</v>
+      <c r="AB7">
+        <v>0</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -17260,21 +17597,18 @@
       <c r="AD7">
         <v>0</v>
       </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="16" t="s">
-        <v>197</v>
+      <c r="AE7" s="16" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E3:AE7">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+  <conditionalFormatting sqref="E3:AD7">
+    <cfRule type="cellIs" dxfId="71" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q3:AE3 B3:E7 I3:M7 Q4:S4 W4:X4 AC4:AE4 N5:AE5 Q6:AE6 Q7:S7 W7:X7 AC7:AE7">
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+  <conditionalFormatting sqref="B3:E7 I3:M7 Q4:S4 W4:X4 AB4:AD4 Q7:S7 W7:X7 AB7:AD7 Q3:AD3 N5:AD5 Q6:AD6">
+    <cfRule type="cellIs" dxfId="70" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17285,7 +17619,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA691ACA-93ED-4815-AE98-5327707E2A32}">
-  <dimension ref="A1:AS31"/>
+  <dimension ref="A1:AR31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="54.44140625" customWidth="1"/>
@@ -17293,7 +17627,7 @@
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" t="s">
         <v>15</v>
@@ -17305,46 +17639,46 @@
         <v>160</v>
       </c>
       <c r="E1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F1" t="s">
         <v>198</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>199</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>376</v>
+      </c>
+      <c r="I1" t="s">
         <v>200</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
+        <v>375</v>
+      </c>
+      <c r="K1" t="s">
+        <v>201</v>
+      </c>
+      <c r="L1" t="s">
+        <v>202</v>
+      </c>
+      <c r="M1" t="s">
+        <v>203</v>
+      </c>
+      <c r="N1" t="s">
         <v>377</v>
       </c>
-      <c r="I1" t="s">
-        <v>201</v>
-      </c>
-      <c r="J1" t="s">
-        <v>376</v>
-      </c>
-      <c r="K1" t="s">
-        <v>202</v>
-      </c>
-      <c r="L1" t="s">
-        <v>203</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>204</v>
       </c>
-      <c r="N1" t="s">
-        <v>378</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>205</v>
       </c>
-      <c r="P1" t="s">
-        <v>206</v>
-      </c>
       <c r="Q1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S1" t="s">
         <v>163</v>
@@ -17362,197 +17696,197 @@
         <v>166</v>
       </c>
       <c r="X1" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y1" t="s">
         <v>207</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>208</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>209</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>210</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>211</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>212</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>213</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>214</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>215</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>216</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>217</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>218</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>219</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>220</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>221</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>222</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>223</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>224</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>225</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>226</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="R2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="S2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="T2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="U2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="V2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="W2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="X2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Y2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Z2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AA2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AB2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AC2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AD2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AE2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AH2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AI2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AJ2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AK2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AL2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AM2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AN2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AO2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AP2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AQ2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AR2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B3" s="16">
         <v>1</v>
@@ -17561,10 +17895,10 @@
         <v>27</v>
       </c>
       <c r="D3" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>230</v>
       </c>
       <c r="F3" s="8">
         <v>0.92</v>
@@ -17686,19 +18020,19 @@
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B4" s="16">
         <v>1</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>230</v>
       </c>
       <c r="F4" s="13">
         <v>1</v>
@@ -17820,7 +18154,7 @@
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B5" s="16">
         <v>1</v>
@@ -17829,10 +18163,10 @@
         <v>27</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F5" s="8">
         <v>0.92</v>
@@ -17954,19 +18288,19 @@
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B6" s="16">
         <v>1</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F6" s="8">
         <v>0.92</v>
@@ -18088,7 +18422,7 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B7" s="16">
         <v>1</v>
@@ -18097,10 +18431,10 @@
         <v>27</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F7" s="13">
         <v>1</v>
@@ -18222,19 +18556,19 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B8" s="16">
         <v>1</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F8" s="8">
         <v>0.92</v>
@@ -18356,7 +18690,7 @@
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B9" s="16">
         <v>1</v>
@@ -18365,10 +18699,10 @@
         <v>27</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F9" s="8">
         <v>1</v>
@@ -18490,19 +18824,19 @@
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B10" s="16">
         <v>1</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F10" s="13">
         <v>1</v>
@@ -18624,7 +18958,7 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B11" s="16">
         <v>1</v>
@@ -18633,10 +18967,10 @@
         <v>27</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F11" s="13">
         <v>1</v>
@@ -18758,7 +19092,7 @@
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B12" s="16">
         <v>1</v>
@@ -18767,10 +19101,10 @@
         <v>27</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F12" s="13">
         <v>1</v>
@@ -18892,19 +19226,19 @@
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B13" s="16">
         <v>1</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F13" s="8">
         <v>0.9</v>
@@ -19026,19 +19360,19 @@
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B14" s="16">
         <v>1</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F14" s="8">
         <v>0.89</v>
@@ -19160,7 +19494,7 @@
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B15" s="16">
         <v>1</v>
@@ -19169,10 +19503,10 @@
         <v>27</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F15" s="13">
         <v>1</v>
@@ -19294,7 +19628,7 @@
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B16" s="16">
         <v>1</v>
@@ -19303,10 +19637,10 @@
         <v>27</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F16" s="8">
         <v>0.75</v>
@@ -19426,9 +19760,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B17" s="16">
         <v>1</v>
@@ -19437,10 +19771,10 @@
         <v>27</v>
       </c>
       <c r="D17" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>251</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>252</v>
       </c>
       <c r="F17" s="16">
         <v>1</v>
@@ -19497,10 +19831,10 @@
         <v>0</v>
       </c>
       <c r="X17" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="Y17" s="16" t="s">
         <v>253</v>
-      </c>
-      <c r="Y17" s="16" t="s">
-        <v>254</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -19560,21 +19894,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B18" s="16">
         <v>1</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D18" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="E18" s="16" t="s">
         <v>251</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>252</v>
       </c>
       <c r="F18" s="16">
         <v>1</v>
@@ -19631,10 +19965,10 @@
         <v>0</v>
       </c>
       <c r="X18" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="Y18" s="16" t="s">
         <v>253</v>
-      </c>
-      <c r="Y18" s="16" t="s">
-        <v>254</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -19694,9 +20028,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B19" s="16">
         <v>1</v>
@@ -19705,10 +20039,10 @@
         <v>27</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F19" s="16">
         <v>1</v>
@@ -19765,10 +20099,10 @@
         <v>0</v>
       </c>
       <c r="X19" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Y19" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -19828,21 +20162,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B20" s="16">
         <v>1</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F20" s="16">
         <v>1</v>
@@ -19899,10 +20233,10 @@
         <v>0</v>
       </c>
       <c r="X20" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Y20" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -19962,21 +20296,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>259</v>
+      </c>
+      <c r="B21" s="16">
+        <v>1</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D21" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="B21" s="16">
-        <v>1</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>261</v>
-      </c>
       <c r="E21" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F21" s="16">
         <v>1</v>
@@ -20033,10 +20367,10 @@
         <v>0</v>
       </c>
       <c r="X21" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Y21" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -20096,21 +20430,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B22" s="16">
+        <v>1</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D22" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="B22" s="16">
-        <v>1</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>264</v>
-      </c>
       <c r="E22" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F22" s="16">
         <v>1</v>
@@ -20167,10 +20501,10 @@
         <v>0</v>
       </c>
       <c r="X22" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Y22" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Z22" s="11">
         <v>0</v>
@@ -20230,9 +20564,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B23" s="16">
         <v>1</v>
@@ -20241,10 +20575,10 @@
         <v>27</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F23" s="16">
         <v>1</v>
@@ -20301,84 +20635,84 @@
         <v>0</v>
       </c>
       <c r="X23" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Y23" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="Z23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="8">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR23" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>267</v>
       </c>
-      <c r="Z23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="8">
-        <v>1</v>
-      </c>
-      <c r="AB23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR23" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:45" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B24" s="16">
+        <v>1</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D24" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="B24" s="16">
-        <v>1</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>269</v>
-      </c>
       <c r="E24" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F24" s="8">
         <v>0.375</v>
@@ -20498,21 +20832,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>269</v>
+      </c>
+      <c r="B25" s="16">
+        <v>1</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="B25" s="16">
-        <v>1</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>271</v>
-      </c>
       <c r="E25" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F25" s="8">
         <v>0.39</v>
@@ -20632,21 +20966,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>271</v>
+      </c>
+      <c r="B26" s="16">
+        <v>1</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D26" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="B26" s="16">
-        <v>1</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>273</v>
-      </c>
       <c r="E26" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F26" s="8">
         <v>0.35</v>
@@ -20766,21 +21100,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>273</v>
+      </c>
+      <c r="B27" s="16">
+        <v>1</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D27" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="B27" s="16">
-        <v>1</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>275</v>
-      </c>
       <c r="E27" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F27" s="8">
         <v>0.35</v>
@@ -20900,52 +21234,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:45" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>276</v>
+    <row r="28" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A28" s="25" t="s">
+        <v>371</v>
       </c>
       <c r="B28" s="16">
         <v>1</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="16"/>
+        <v>196</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>372</v>
+      </c>
       <c r="E28" s="16" t="s">
-        <v>230</v>
+        <v>373</v>
       </c>
       <c r="F28" s="8">
-        <v>0.78500000000000003</v>
-      </c>
-      <c r="G28" s="15">
-        <v>0</v>
-      </c>
-      <c r="H28" s="15">
-        <v>0</v>
-      </c>
-      <c r="I28" s="15">
-        <v>0</v>
-      </c>
-      <c r="J28" s="15">
-        <v>0</v>
-      </c>
-      <c r="K28" s="15">
-        <v>0</v>
-      </c>
-      <c r="L28" s="15">
-        <v>0</v>
-      </c>
-      <c r="M28" s="15">
-        <v>0</v>
-      </c>
-      <c r="N28" s="15">
+        <v>3.5</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="H28" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="I28" s="25">
+        <v>0</v>
+      </c>
+      <c r="J28" s="25">
+        <v>0</v>
+      </c>
+      <c r="K28" s="25">
+        <v>0</v>
+      </c>
+      <c r="L28" s="25">
+        <v>0</v>
+      </c>
+      <c r="M28" s="25">
+        <v>0</v>
+      </c>
+      <c r="N28" s="25">
         <v>0</v>
       </c>
       <c r="O28" s="8">
-        <v>1.3</v>
-      </c>
-      <c r="P28" s="15">
-        <v>0</v>
+        <v>347</v>
+      </c>
+      <c r="P28" s="8">
+        <v>225</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -20954,87 +21290,87 @@
         <v>10000</v>
       </c>
       <c r="S28" s="8">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="T28" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28">
-        <v>0</v>
-      </c>
-      <c r="AI28">
-        <v>0</v>
-      </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>0</v>
-      </c>
-      <c r="AN28">
-        <v>0</v>
-      </c>
-      <c r="AO28">
-        <v>0</v>
-      </c>
-      <c r="AP28">
-        <v>0</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="U28" s="16">
+        <v>0</v>
+      </c>
+      <c r="V28" s="16">
+        <v>0</v>
+      </c>
+      <c r="W28" s="16">
+        <v>0</v>
+      </c>
+      <c r="X28" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AR28" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B29" s="16">
         <v>1</v>
@@ -21044,10 +21380,10 @@
       </c>
       <c r="D29" s="16"/>
       <c r="E29" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F29" s="8">
-        <v>0.83</v>
+        <v>0.78500000000000003</v>
       </c>
       <c r="G29" s="15">
         <v>0</v>
@@ -21074,7 +21410,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="8">
-        <v>10</v>
+        <v>1.3</v>
       </c>
       <c r="P29" s="15">
         <v>0</v>
@@ -21086,7 +21422,7 @@
         <v>10000</v>
       </c>
       <c r="S29" s="8">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="T29" s="16">
         <v>1.0000000000000001E-5</v>
@@ -21164,27 +21500,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B30" s="16">
         <v>1</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>279</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F30" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="G30" s="8">
-        <v>0.5</v>
+        <v>0.83</v>
+      </c>
+      <c r="G30" s="15">
+        <v>0</v>
       </c>
       <c r="H30" s="15">
         <v>0</v>
@@ -21210,7 +21544,7 @@
       <c r="O30" s="8">
         <v>10</v>
       </c>
-      <c r="P30" s="13">
+      <c r="P30" s="15">
         <v>0</v>
       </c>
       <c r="Q30">
@@ -21220,7 +21554,7 @@
         <v>10000</v>
       </c>
       <c r="S30" s="8">
-        <v>480</v>
+        <v>67</v>
       </c>
       <c r="T30" s="16">
         <v>1.0000000000000001E-5</v>
@@ -21298,41 +21632,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:45" x14ac:dyDescent="0.3">
-      <c r="A31" s="25" t="s">
-        <v>372</v>
-      </c>
-      <c r="B31" s="25">
-        <v>1</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="E31" s="25" t="s">
-        <v>374</v>
-      </c>
-      <c r="F31" s="25">
-        <v>3.5</v>
-      </c>
-      <c r="G31" s="25">
-        <v>0.375</v>
-      </c>
-      <c r="H31" s="25">
-        <v>0.8</v>
-      </c>
-      <c r="I31" s="25">
-        <v>0.57499999999999996</v>
+    <row r="31" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>277</v>
+      </c>
+      <c r="B31" s="16">
+        <v>1</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
+      </c>
+      <c r="I31" s="15">
+        <v>0</v>
       </c>
       <c r="J31" s="15">
         <v>0</v>
       </c>
-      <c r="K31" s="25">
-        <v>0</v>
-      </c>
-      <c r="L31" s="25">
+      <c r="K31" s="15">
+        <v>0</v>
+      </c>
+      <c r="L31" s="15">
         <v>0</v>
       </c>
       <c r="M31" s="15">
@@ -21341,178 +21675,170 @@
       <c r="N31" s="15">
         <v>0</v>
       </c>
-      <c r="O31" s="25">
-        <v>0</v>
-      </c>
-      <c r="P31" s="25">
-        <v>347</v>
-      </c>
-      <c r="Q31" s="25">
-        <v>225</v>
-      </c>
-      <c r="R31" s="25">
-        <v>0</v>
-      </c>
-      <c r="S31" s="25">
+      <c r="O31" s="8">
+        <v>10</v>
+      </c>
+      <c r="P31" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31" s="16">
         <v>10000</v>
       </c>
-      <c r="T31" s="25">
-        <v>129</v>
-      </c>
-      <c r="U31" s="25">
+      <c r="S31" s="8">
+        <v>480</v>
+      </c>
+      <c r="T31" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="V31" s="25">
-        <v>0</v>
-      </c>
-      <c r="W31" s="25">
-        <v>0</v>
-      </c>
-      <c r="X31" s="25">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="25">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AE31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AF31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AG31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AH31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AI31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AK31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AL31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AM31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AN31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AO31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AP31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AQ31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AR31" s="25">
-        <v>0</v>
-      </c>
-      <c r="AS31" s="25">
+      <c r="U31" s="16">
+        <v>0</v>
+      </c>
+      <c r="V31" s="16">
+        <v>0</v>
+      </c>
+      <c r="W31" s="16">
+        <v>0</v>
+      </c>
+      <c r="X31" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="16">
+        <v>0</v>
+      </c>
+      <c r="AR31" s="16">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B23:E30">
-    <cfRule type="cellIs" dxfId="17" priority="11" operator="equal">
+  <conditionalFormatting sqref="B23:E28 T31:AR31 T28 B31:E31 B29:C30 E29:E30">
+    <cfRule type="cellIs" dxfId="69" priority="12" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22">
-    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="9" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22">
-    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="8" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K10:L30 J10:J31 F3:AR3 F4:G30 O4:AR30 M4:N31 I4:L9 I10:I30 H4:H31">
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
+  <conditionalFormatting sqref="F3:AR27 F29:AR31 F28:T28">
+    <cfRule type="cellIs" dxfId="66" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:Q30">
-    <cfRule type="cellIs" dxfId="13" priority="16" operator="equal">
+  <conditionalFormatting sqref="Q4:Q31">
+    <cfRule type="cellIs" dxfId="65" priority="17" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q3:R3">
-    <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="16" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R8:R9 B8:E9">
-    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="15" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R13:R14 U13:Z21 AE13:AR21 R16:R21 B13:E21">
-    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="13" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R23:R30 U23:Z30 AE23:AR30">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+  <conditionalFormatting sqref="R23:R31 U23:Z27 AE23:AR27 AE29:AR31 U29:Z31">
+    <cfRule type="cellIs" dxfId="61" priority="11" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U3:AR6 R5:R6 U8:AR9 AA13:AD16 AB19:AB21 AC21:AD21 AB23 AA24:AD30 B3:E6">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+  <conditionalFormatting sqref="U3:AR6 R5:R6 U8:AR9 AA13:AD16 AB19:AB21 AC21:AD21 AB23 AA24:AD27 B3:E6 AA29:AD31">
+    <cfRule type="cellIs" dxfId="60" priority="10" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC17:AD18">
-    <cfRule type="cellIs" dxfId="7" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="14" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31:E31">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+  <conditionalFormatting sqref="B28:E28">
+    <cfRule type="cellIs" dxfId="58" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31:G31 K31:L31 O31:AS31 I31">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+  <conditionalFormatting sqref="F28:G28 K28:L28 I28">
+    <cfRule type="cellIs" dxfId="57" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R31">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+  <conditionalFormatting sqref="R28">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S31 V31:AA31 AF31:AS31">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB31:AE31">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+  <conditionalFormatting sqref="R28">
+    <cfRule type="cellIs" dxfId="53" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21530,19 +21856,19 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B1" t="s">
         <v>15</v>
       </c>
       <c r="C1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F1" t="s">
         <v>163</v>
@@ -21560,52 +21886,52 @@
         <v>166</v>
       </c>
       <c r="K1" t="s">
+        <v>280</v>
+      </c>
+      <c r="L1" t="s">
         <v>281</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>282</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>283</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>284</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>285</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>286</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>287</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
+        <v>200</v>
+      </c>
+      <c r="T1" t="s">
+        <v>201</v>
+      </c>
+      <c r="U1" t="s">
+        <v>203</v>
+      </c>
+      <c r="V1" t="s">
+        <v>204</v>
+      </c>
+      <c r="W1" t="s">
         <v>288</v>
       </c>
-      <c r="S1" t="s">
-        <v>201</v>
-      </c>
-      <c r="T1" t="s">
-        <v>202</v>
-      </c>
-      <c r="U1" t="s">
-        <v>204</v>
-      </c>
-      <c r="V1" t="s">
-        <v>205</v>
-      </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>289</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z1" t="s">
         <v>290</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>291</v>
       </c>
       <c r="AA1" t="s">
         <v>22</v>
@@ -21613,96 +21939,96 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="R2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="S2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="T2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="U2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="V2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="W2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="X2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Y2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Z2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AA2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B3" s="16">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>292</v>
-      </c>
-      <c r="B3" s="16">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>293</v>
       </c>
       <c r="D3" s="16">
         <v>0</v>
@@ -21779,13 +22105,13 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B4" s="16">
         <v>1</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D4" s="16">
         <v>0</v>
@@ -21862,13 +22188,13 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B5" s="16">
         <v>1</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D5" s="16">
         <v>0</v>
@@ -21945,13 +22271,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B6" s="16">
         <v>1</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D6" s="16">
         <v>0</v>
@@ -22023,18 +22349,18 @@
         <v>0</v>
       </c>
       <c r="AA6" s="16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B7" s="16">
         <v>1</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D7" s="16">
         <v>0</v>
@@ -22111,13 +22437,13 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B8" s="16">
         <v>1</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D8" s="16">
         <v>0</v>
@@ -22189,7 +22515,7 @@
         <v>0</v>
       </c>
       <c r="AA8" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -22207,34 +22533,34 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B1" t="s">
         <v>15</v>
       </c>
       <c r="C1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E1" t="s">
         <v>116</v>
       </c>
       <c r="F1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K1" t="s">
         <v>163</v>
@@ -22254,60 +22580,60 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B3" s="16">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>302</v>
-      </c>
-      <c r="B3" s="16">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>303</v>
       </c>
       <c r="D3" s="16">
         <v>1</v>
@@ -22348,13 +22674,13 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B4" s="16">
         <v>1</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D4" s="16">
         <v>1</v>
@@ -22395,13 +22721,13 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B5" s="16">
         <v>1</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -22442,13 +22768,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B6" s="16">
         <v>1</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D6" s="16">
         <v>1</v>
@@ -22489,13 +22815,13 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B7" s="16">
         <v>1</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D7" s="16">
         <v>1</v>
@@ -22536,13 +22862,13 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B8" s="16">
         <v>1</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D8" s="16">
         <v>1</v>
@@ -22581,15 +22907,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>309</v>
+    <row r="9" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="25" t="s">
+        <v>374</v>
       </c>
       <c r="B9" s="16">
         <v>1</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D9" s="16">
         <v>1</v>
@@ -22630,13 +22956,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B10" s="16">
         <v>1</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D10" s="16">
         <v>1</v>
@@ -22677,13 +23003,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B11" s="16">
         <v>1</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D11" s="16">
         <v>1</v>
@@ -22724,13 +23050,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B12" s="16">
         <v>1</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D12" s="16">
         <v>1</v>
@@ -22771,13 +23097,13 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B13" s="16">
         <v>1</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D13" s="16">
         <v>1</v>
@@ -22818,13 +23144,13 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B14" s="16">
         <v>1</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D14" s="16">
         <v>1</v>
@@ -22864,14 +23190,14 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
-        <v>315</v>
+      <c r="A15" t="s">
+        <v>313</v>
       </c>
       <c r="B15" s="16">
         <v>1</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D15" s="16">
         <v>1</v>
@@ -22912,13 +23238,13 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B16" s="16">
         <v>1</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D16" s="16">
         <v>1</v>
@@ -22959,13 +23285,13 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B17" s="16">
         <v>1</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D17" s="16">
         <v>1</v>
@@ -23006,13 +23332,13 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B18" s="16">
         <v>1</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D18" s="16">
         <v>1</v>
@@ -23053,13 +23379,13 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B19" s="16">
         <v>1</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D19" s="16">
         <v>1</v>
@@ -23100,13 +23426,13 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B20" s="16">
         <v>1</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D20" s="16">
         <v>1</v>
@@ -23147,13 +23473,13 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B21" s="16">
         <v>1</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D21" s="16">
         <v>1</v>
@@ -23193,49 +23519,49 @@
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="25" t="s">
-        <v>375</v>
-      </c>
-      <c r="B22" s="25">
-        <v>1</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>303</v>
-      </c>
-      <c r="D22" s="25">
-        <v>1</v>
-      </c>
-      <c r="E22" s="25">
-        <v>0</v>
-      </c>
-      <c r="F22" s="25">
-        <v>0</v>
-      </c>
-      <c r="G22" s="25">
-        <v>0</v>
-      </c>
-      <c r="H22" s="25">
+      <c r="A22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="B22" s="16">
+        <v>1</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="D22" s="16">
+        <v>1</v>
+      </c>
+      <c r="E22" s="16">
+        <v>0</v>
+      </c>
+      <c r="F22" s="16">
+        <v>0</v>
+      </c>
+      <c r="G22" s="16">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16">
         <v>9999</v>
       </c>
-      <c r="I22" s="25">
-        <v>0</v>
-      </c>
-      <c r="J22" s="25">
-        <v>0</v>
-      </c>
-      <c r="K22" s="25">
+      <c r="I22" s="16">
+        <v>0</v>
+      </c>
+      <c r="J22" s="16">
+        <v>0</v>
+      </c>
+      <c r="K22" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="L22" s="25">
+      <c r="L22" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M22" s="25">
-        <v>0</v>
-      </c>
-      <c r="N22" s="25">
-        <v>0</v>
-      </c>
-      <c r="O22" s="25">
+      <c r="M22" s="16">
+        <v>0</v>
+      </c>
+      <c r="N22" s="16">
+        <v>0</v>
+      </c>
+      <c r="O22" s="16">
         <v>0</v>
       </c>
     </row>

--- a/template_examples/standard_parameters_example.xlsx
+++ b/template_examples/standard_parameters_example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TimSteinort\Documents\GitHub\SESMG\template_examples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JanBaumeister\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3751620C-06B1-49B6-B1AB-1B387232969D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD63C7B-0E4A-4F38-B151-02DAE5ED6741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="10" xr2:uid="{D48BE4BC-BA48-4DC0-B3DF-D04B8CFD99C7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="6" xr2:uid="{D48BE4BC-BA48-4DC0-B3DF-D04B8CFD99C7}"/>
   </bookViews>
   <sheets>
     <sheet name="energysystem" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="7_insulation" sheetId="10" r:id="rId10"/>
     <sheet name="8_district_heat_network" sheetId="12" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="380">
   <si>
     <t>start date</t>
   </si>
@@ -1159,6 +1159,33 @@
   </si>
   <si>
     <t>dh_heatstation</t>
+  </si>
+  <si>
+    <t>hydrogen bus combined heat and power central</t>
+  </si>
+  <si>
+    <t>electricity bus combined heat and power natural gas hydrogen central</t>
+  </si>
+  <si>
+    <t>combined heat and power natural gas hydrogen central</t>
+  </si>
+  <si>
+    <t>natural_gas_hydrogen_CHP</t>
+  </si>
+  <si>
+    <t>GenericTwoInputTransformer</t>
+  </si>
+  <si>
+    <t>input2 / input</t>
+  </si>
+  <si>
+    <t>electricity combined heat and power natural gas hydrogen central link central</t>
+  </si>
+  <si>
+    <t>variable input costs 2</t>
+  </si>
+  <si>
+    <t>variable input constraint costs 2</t>
   </si>
 </sst>
 </file>
@@ -1406,11 +1433,137 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 3" xfId="1" xr:uid="{3EB3DAA0-9F71-48CB-8FEA-1E1CAF40E04C}"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="40">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1516,6 +1669,20 @@
       <fill>
         <patternFill>
           <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1858,19 +2025,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9349B1DA-DD91-4E08-AB6A-4F16A6735056}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.7265625" customWidth="1"/>
+    <col min="6" max="6" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1902,7 +2069,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -1934,7 +2101,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>40909</v>
       </c>
@@ -1974,12 +2141,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0876A1A-D601-4F49-AE30-77EB630A1DC1}">
   <dimension ref="A1:D116"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -1993,7 +2160,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -2007,7 +2174,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>144</v>
       </c>
@@ -2021,7 +2188,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1919</v>
       </c>
@@ -2035,7 +2202,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1920</v>
       </c>
@@ -2049,7 +2216,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1921</v>
       </c>
@@ -2063,7 +2230,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1922</v>
       </c>
@@ -2077,7 +2244,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1923</v>
       </c>
@@ -2091,7 +2258,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1924</v>
       </c>
@@ -2105,7 +2272,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1925</v>
       </c>
@@ -2119,7 +2286,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1926</v>
       </c>
@@ -2133,7 +2300,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1927</v>
       </c>
@@ -2147,7 +2314,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1928</v>
       </c>
@@ -2161,7 +2328,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1929</v>
       </c>
@@ -2175,7 +2342,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1930</v>
       </c>
@@ -2189,7 +2356,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1931</v>
       </c>
@@ -2203,7 +2370,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1932</v>
       </c>
@@ -2217,7 +2384,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1933</v>
       </c>
@@ -2231,7 +2398,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1934</v>
       </c>
@@ -2245,7 +2412,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1935</v>
       </c>
@@ -2259,7 +2426,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1936</v>
       </c>
@@ -2273,7 +2440,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1937</v>
       </c>
@@ -2287,7 +2454,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1938</v>
       </c>
@@ -2301,7 +2468,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1939</v>
       </c>
@@ -2315,7 +2482,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1940</v>
       </c>
@@ -2329,7 +2496,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>1941</v>
       </c>
@@ -2343,7 +2510,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1942</v>
       </c>
@@ -2357,7 +2524,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1943</v>
       </c>
@@ -2371,7 +2538,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1944</v>
       </c>
@@ -2385,7 +2552,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1945</v>
       </c>
@@ -2399,7 +2566,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>1946</v>
       </c>
@@ -2413,7 +2580,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1947</v>
       </c>
@@ -2427,7 +2594,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1948</v>
       </c>
@@ -2441,7 +2608,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>1949</v>
       </c>
@@ -2455,7 +2622,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1950</v>
       </c>
@@ -2469,7 +2636,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>1951</v>
       </c>
@@ -2483,7 +2650,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>1952</v>
       </c>
@@ -2497,7 +2664,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>1953</v>
       </c>
@@ -2511,7 +2678,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>1954</v>
       </c>
@@ -2525,7 +2692,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1955</v>
       </c>
@@ -2539,7 +2706,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>1956</v>
       </c>
@@ -2553,7 +2720,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1957</v>
       </c>
@@ -2567,7 +2734,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>1958</v>
       </c>
@@ -2581,7 +2748,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>1959</v>
       </c>
@@ -2595,7 +2762,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>1960</v>
       </c>
@@ -2609,7 +2776,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>1961</v>
       </c>
@@ -2623,7 +2790,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>1962</v>
       </c>
@@ -2637,7 +2804,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>1963</v>
       </c>
@@ -2651,7 +2818,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>1964</v>
       </c>
@@ -2665,7 +2832,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>1965</v>
       </c>
@@ -2679,7 +2846,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>1966</v>
       </c>
@@ -2693,7 +2860,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>1967</v>
       </c>
@@ -2707,7 +2874,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>1968</v>
       </c>
@@ -2721,7 +2888,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>1969</v>
       </c>
@@ -2735,7 +2902,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>1970</v>
       </c>
@@ -2749,7 +2916,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>1971</v>
       </c>
@@ -2763,7 +2930,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>1972</v>
       </c>
@@ -2777,7 +2944,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>1973</v>
       </c>
@@ -2791,7 +2958,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>1974</v>
       </c>
@@ -2805,7 +2972,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>1975</v>
       </c>
@@ -2819,7 +2986,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>1976</v>
       </c>
@@ -2833,7 +3000,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>1977</v>
       </c>
@@ -2847,7 +3014,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>1978</v>
       </c>
@@ -2861,7 +3028,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>1979</v>
       </c>
@@ -2875,7 +3042,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>1980</v>
       </c>
@@ -2889,7 +3056,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>1981</v>
       </c>
@@ -2903,7 +3070,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>1982</v>
       </c>
@@ -2917,7 +3084,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>1983</v>
       </c>
@@ -2931,7 +3098,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>1984</v>
       </c>
@@ -2945,7 +3112,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>1985</v>
       </c>
@@ -2959,7 +3126,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>1986</v>
       </c>
@@ -2973,7 +3140,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>1987</v>
       </c>
@@ -2987,7 +3154,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>1988</v>
       </c>
@@ -3001,7 +3168,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>1989</v>
       </c>
@@ -3015,7 +3182,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>1990</v>
       </c>
@@ -3029,7 +3196,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>1991</v>
       </c>
@@ -3043,7 +3210,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>1992</v>
       </c>
@@ -3057,7 +3224,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>1993</v>
       </c>
@@ -3071,7 +3238,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>1994</v>
       </c>
@@ -3085,7 +3252,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>1995</v>
       </c>
@@ -3099,7 +3266,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>1996</v>
       </c>
@@ -3113,7 +3280,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>1997</v>
       </c>
@@ -3127,7 +3294,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>1998</v>
       </c>
@@ -3141,7 +3308,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>1999</v>
       </c>
@@ -3155,7 +3322,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>2000</v>
       </c>
@@ -3169,7 +3336,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>2001</v>
       </c>
@@ -3183,7 +3350,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>2002</v>
       </c>
@@ -3197,7 +3364,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>2003</v>
       </c>
@@ -3211,7 +3378,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>2004</v>
       </c>
@@ -3225,7 +3392,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>2005</v>
       </c>
@@ -3239,7 +3406,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>2006</v>
       </c>
@@ -3253,7 +3420,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>2007</v>
       </c>
@@ -3267,7 +3434,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>2008</v>
       </c>
@@ -3281,7 +3448,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>2009</v>
       </c>
@@ -3295,7 +3462,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>2010</v>
       </c>
@@ -3309,7 +3476,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>2011</v>
       </c>
@@ -3323,7 +3490,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>2012</v>
       </c>
@@ -3337,7 +3504,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>2013</v>
       </c>
@@ -3351,7 +3518,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>2014</v>
       </c>
@@ -3365,7 +3532,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>2015</v>
       </c>
@@ -3379,7 +3546,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>2016</v>
       </c>
@@ -3393,7 +3560,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>2017</v>
       </c>
@@ -3407,7 +3574,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>2018</v>
       </c>
@@ -3421,7 +3588,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>2019</v>
       </c>
@@ -3435,7 +3602,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>2020</v>
       </c>
@@ -3449,7 +3616,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>2021</v>
       </c>
@@ -3463,7 +3630,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>2022</v>
       </c>
@@ -3477,7 +3644,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>2023</v>
       </c>
@@ -3491,7 +3658,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>2024</v>
       </c>
@@ -3505,7 +3672,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>2025</v>
       </c>
@@ -3519,7 +3686,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>325</v>
       </c>
@@ -3533,7 +3700,7 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>326</v>
       </c>
@@ -3547,7 +3714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>163</v>
       </c>
@@ -3561,7 +3728,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>327</v>
       </c>
@@ -3575,7 +3742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>164</v>
       </c>
@@ -3589,7 +3756,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>328</v>
       </c>
@@ -3621,20 +3788,20 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EEE9DEA-E38F-C741-B378-A7CB5600BE5E}">
   <dimension ref="A1:O33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>329</v>
       </c>
@@ -3681,7 +3848,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>356</v>
       </c>
@@ -3728,7 +3895,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>337</v>
       </c>
@@ -3775,7 +3942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>338</v>
       </c>
@@ -3822,7 +3989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>339</v>
       </c>
@@ -3869,7 +4036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>340</v>
       </c>
@@ -3916,7 +4083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>341</v>
       </c>
@@ -3963,7 +4130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>342</v>
       </c>
@@ -4010,7 +4177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>343</v>
       </c>
@@ -4057,7 +4224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>344</v>
       </c>
@@ -4104,7 +4271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>345</v>
       </c>
@@ -4151,7 +4318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>346</v>
       </c>
@@ -4198,7 +4365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>347</v>
       </c>
@@ -4245,7 +4412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>348</v>
       </c>
@@ -4292,7 +4459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="20" t="s">
         <v>350</v>
       </c>
@@ -4339,7 +4506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="20" t="s">
         <v>357</v>
       </c>
@@ -4386,7 +4553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="20" t="s">
         <v>358</v>
       </c>
@@ -4433,7 +4600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
         <v>359</v>
       </c>
@@ -4480,7 +4647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
         <v>360</v>
       </c>
@@ -4527,7 +4694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="20" t="s">
         <v>351</v>
       </c>
@@ -4574,7 +4741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="20" t="s">
         <v>361</v>
       </c>
@@ -4621,7 +4788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="20" t="s">
         <v>362</v>
       </c>
@@ -4668,7 +4835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="20" t="s">
         <v>363</v>
       </c>
@@ -4715,7 +4882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="20" t="s">
         <v>352</v>
       </c>
@@ -4762,7 +4929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="20" t="s">
         <v>364</v>
       </c>
@@ -4809,7 +4976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="20" t="s">
         <v>353</v>
       </c>
@@ -4856,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="20" t="s">
         <v>365</v>
       </c>
@@ -4903,7 +5070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="20" t="s">
         <v>366</v>
       </c>
@@ -4950,7 +5117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="20" t="s">
         <v>367</v>
       </c>
@@ -4997,7 +5164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="20" t="s">
         <v>368</v>
       </c>
@@ -5042,7 +5209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>354</v>
       </c>
@@ -5089,7 +5256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>355</v>
       </c>
@@ -5136,7 +5303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>370</v>
       </c>
@@ -5192,14 +5359,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6075F4E-6449-42F6-B0A2-E3B463F49D3C}">
-  <dimension ref="A1:I39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="53.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53.1796875" customWidth="1"/>
+    <col min="6" max="6" width="12.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -5228,7 +5395,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -5257,7 +5424,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -5286,7 +5453,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -5315,7 +5482,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -5344,7 +5511,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -5373,7 +5540,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -5402,7 +5569,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -5431,7 +5598,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -5460,7 +5627,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -5489,7 +5656,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -5518,7 +5685,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -5547,7 +5714,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="24" t="s">
         <v>35</v>
       </c>
@@ -5576,7 +5743,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -5605,7 +5772,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -5634,7 +5801,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -5663,7 +5830,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -5692,7 +5859,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -5721,7 +5888,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -5750,7 +5917,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -5779,7 +5946,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -5808,7 +5975,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -5837,7 +6004,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -5866,7 +6033,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -5895,7 +6062,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -5924,7 +6091,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -5953,7 +6120,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -5982,7 +6149,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -6011,7 +6178,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>51</v>
       </c>
@@ -6040,7 +6207,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>52</v>
       </c>
@@ -6069,7 +6236,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -6098,7 +6265,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>54</v>
       </c>
@@ -6127,7 +6294,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>55</v>
       </c>
@@ -6156,7 +6323,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -6185,7 +6352,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>57</v>
       </c>
@@ -6214,7 +6381,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
         <v>58</v>
       </c>
@@ -6243,7 +6410,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
         <v>59</v>
       </c>
@@ -6272,7 +6439,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
         <v>61</v>
       </c>
@@ -6301,7 +6468,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>62</v>
       </c>
@@ -6330,22 +6497,88 @@
         <v>12</v>
       </c>
     </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>371</v>
+      </c>
+      <c r="B40" s="16">
+        <v>1</v>
+      </c>
+      <c r="C40" s="16">
+        <v>0</v>
+      </c>
+      <c r="D40" s="16">
+        <v>1</v>
+      </c>
+      <c r="E40" s="16">
+        <v>0</v>
+      </c>
+      <c r="F40" s="8">
+        <v>0.15620000000000001</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40" s="8">
+        <v>44</v>
+      </c>
+      <c r="I40" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>372</v>
+      </c>
+      <c r="B41" s="16">
+        <v>1</v>
+      </c>
+      <c r="C41" s="16">
+        <v>1</v>
+      </c>
+      <c r="D41" s="16">
+        <v>0</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-6.8199999999999997E-2</v>
+      </c>
+      <c r="F41" s="8">
+        <v>0</v>
+      </c>
+      <c r="G41" s="8">
+        <v>-140</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B3:B22 B24:B35">
-    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="6" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B39">
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+  <conditionalFormatting sqref="B39:B41">
+    <cfRule type="cellIs" dxfId="38" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:H39">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="4" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40:H41">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6357,13 +6590,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A343EB-B652-4B18-B41E-28ABD2CDDDDD}">
   <dimension ref="A1:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -6395,7 +6628,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>356</v>
       </c>
@@ -6427,7 +6660,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -6459,7 +6692,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -6491,7 +6724,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -6523,7 +6756,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>76</v>
       </c>
@@ -6555,7 +6788,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -6587,7 +6820,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -6619,7 +6852,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -6651,7 +6884,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -6683,7 +6916,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>86</v>
       </c>
@@ -6715,7 +6948,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>88</v>
       </c>
@@ -6747,7 +6980,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>90</v>
       </c>
@@ -6779,7 +7012,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -6811,7 +7044,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -6843,7 +7076,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -6875,7 +7108,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -6907,7 +7140,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -6939,7 +7172,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -6971,7 +7204,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>101</v>
       </c>
@@ -7003,7 +7236,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -7035,7 +7268,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>103</v>
       </c>
@@ -7067,7 +7300,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>104</v>
       </c>
@@ -7099,7 +7332,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>105</v>
       </c>
@@ -7131,7 +7364,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>106</v>
       </c>
@@ -7163,7 +7396,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>107</v>
       </c>
@@ -7195,7 +7428,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>108</v>
       </c>
@@ -7227,7 +7460,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>109</v>
       </c>
@@ -7259,7 +7492,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>110</v>
       </c>
@@ -7291,7 +7524,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>111</v>
       </c>
@@ -7323,7 +7556,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>113</v>
       </c>
@@ -7355,7 +7588,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>114</v>
       </c>
@@ -7387,7 +7620,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>115</v>
       </c>
@@ -7428,12 +7661,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99D5AF32-1322-42FA-A3FF-C17883258B40}">
   <dimension ref="A1:Z110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="25" max="25" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>117</v>
       </c>
@@ -7513,7 +7746,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>356</v>
       </c>
@@ -7593,7 +7826,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>144</v>
       </c>
@@ -7673,7 +7906,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1919</v>
       </c>
@@ -7753,7 +7986,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1920</v>
       </c>
@@ -7833,7 +8066,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1921</v>
       </c>
@@ -7913,7 +8146,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1922</v>
       </c>
@@ -7993,7 +8226,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1923</v>
       </c>
@@ -8073,7 +8306,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1924</v>
       </c>
@@ -8153,7 +8386,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1925</v>
       </c>
@@ -8233,7 +8466,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1926</v>
       </c>
@@ -8313,7 +8546,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1927</v>
       </c>
@@ -8393,7 +8626,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1928</v>
       </c>
@@ -8473,7 +8706,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1929</v>
       </c>
@@ -8553,7 +8786,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1930</v>
       </c>
@@ -8633,7 +8866,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1931</v>
       </c>
@@ -8713,7 +8946,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1932</v>
       </c>
@@ -8793,7 +9026,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1933</v>
       </c>
@@ -8873,7 +9106,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1934</v>
       </c>
@@ -8953,7 +9186,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1935</v>
       </c>
@@ -9033,7 +9266,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1936</v>
       </c>
@@ -9113,7 +9346,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1937</v>
       </c>
@@ -9193,7 +9426,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1938</v>
       </c>
@@ -9273,7 +9506,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1939</v>
       </c>
@@ -9353,7 +9586,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1940</v>
       </c>
@@ -9433,7 +9666,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>1941</v>
       </c>
@@ -9513,7 +9746,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1942</v>
       </c>
@@ -9593,7 +9826,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1943</v>
       </c>
@@ -9673,7 +9906,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1944</v>
       </c>
@@ -9753,7 +9986,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1945</v>
       </c>
@@ -9833,7 +10066,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>1946</v>
       </c>
@@ -9913,7 +10146,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1947</v>
       </c>
@@ -9993,7 +10226,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1948</v>
       </c>
@@ -10073,7 +10306,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>1949</v>
       </c>
@@ -10153,7 +10386,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1950</v>
       </c>
@@ -10233,7 +10466,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>1951</v>
       </c>
@@ -10313,7 +10546,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>1952</v>
       </c>
@@ -10393,7 +10626,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>1953</v>
       </c>
@@ -10473,7 +10706,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>1954</v>
       </c>
@@ -10553,7 +10786,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1955</v>
       </c>
@@ -10633,7 +10866,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>1956</v>
       </c>
@@ -10713,7 +10946,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1957</v>
       </c>
@@ -10793,7 +11026,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>1958</v>
       </c>
@@ -10873,7 +11106,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>1959</v>
       </c>
@@ -10953,7 +11186,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>1960</v>
       </c>
@@ -11033,7 +11266,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>1961</v>
       </c>
@@ -11113,7 +11346,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>1962</v>
       </c>
@@ -11193,7 +11426,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>1963</v>
       </c>
@@ -11273,7 +11506,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>1964</v>
       </c>
@@ -11353,7 +11586,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>1965</v>
       </c>
@@ -11433,7 +11666,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>1966</v>
       </c>
@@ -11513,7 +11746,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>1967</v>
       </c>
@@ -11593,7 +11826,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>1968</v>
       </c>
@@ -11673,7 +11906,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>1969</v>
       </c>
@@ -11753,7 +11986,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>1970</v>
       </c>
@@ -11833,7 +12066,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>1971</v>
       </c>
@@ -11913,7 +12146,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>1972</v>
       </c>
@@ -11993,7 +12226,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>1973</v>
       </c>
@@ -12073,7 +12306,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>1974</v>
       </c>
@@ -12153,7 +12386,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>1975</v>
       </c>
@@ -12233,7 +12466,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>1976</v>
       </c>
@@ -12313,7 +12546,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>1977</v>
       </c>
@@ -12393,7 +12626,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>1978</v>
       </c>
@@ -12473,7 +12706,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>1979</v>
       </c>
@@ -12553,7 +12786,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>1980</v>
       </c>
@@ -12633,7 +12866,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>1981</v>
       </c>
@@ -12713,7 +12946,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>1982</v>
       </c>
@@ -12793,7 +13026,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>1983</v>
       </c>
@@ -12873,7 +13106,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>1984</v>
       </c>
@@ -12953,7 +13186,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>1985</v>
       </c>
@@ -13033,7 +13266,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>1986</v>
       </c>
@@ -13113,7 +13346,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>1987</v>
       </c>
@@ -13193,7 +13426,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>1988</v>
       </c>
@@ -13273,7 +13506,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>1989</v>
       </c>
@@ -13353,7 +13586,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>1990</v>
       </c>
@@ -13433,7 +13666,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>1991</v>
       </c>
@@ -13513,7 +13746,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>1992</v>
       </c>
@@ -13593,7 +13826,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>1993</v>
       </c>
@@ -13673,7 +13906,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>1994</v>
       </c>
@@ -13753,7 +13986,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>1995</v>
       </c>
@@ -13833,7 +14066,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>1996</v>
       </c>
@@ -13913,7 +14146,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>1997</v>
       </c>
@@ -13993,7 +14226,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>1998</v>
       </c>
@@ -14073,7 +14306,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>1999</v>
       </c>
@@ -14153,7 +14386,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>2000</v>
       </c>
@@ -14233,7 +14466,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>2001</v>
       </c>
@@ -14313,7 +14546,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>2002</v>
       </c>
@@ -14393,7 +14626,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>2003</v>
       </c>
@@ -14473,7 +14706,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>2004</v>
       </c>
@@ -14553,7 +14786,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>2005</v>
       </c>
@@ -14633,7 +14866,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>2006</v>
       </c>
@@ -14713,7 +14946,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>2007</v>
       </c>
@@ -14793,7 +15026,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>2008</v>
       </c>
@@ -14873,7 +15106,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>2009</v>
       </c>
@@ -14953,7 +15186,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>2010</v>
       </c>
@@ -15033,7 +15266,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>2011</v>
       </c>
@@ -15113,7 +15346,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>2012</v>
       </c>
@@ -15193,7 +15426,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>2013</v>
       </c>
@@ -15273,7 +15506,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>2014</v>
       </c>
@@ -15353,7 +15586,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>2015</v>
       </c>
@@ -15433,7 +15666,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>2016</v>
       </c>
@@ -15513,7 +15746,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>2017</v>
       </c>
@@ -15593,7 +15826,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>2018</v>
       </c>
@@ -15673,7 +15906,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>2019</v>
       </c>
@@ -15753,7 +15986,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>2020</v>
       </c>
@@ -15833,7 +16066,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>2021</v>
       </c>
@@ -15913,7 +16146,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>2022</v>
       </c>
@@ -15993,7 +16226,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>2023</v>
       </c>
@@ -16073,7 +16306,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>2024</v>
       </c>
@@ -16153,7 +16386,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>2025</v>
       </c>
@@ -16235,7 +16468,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3:A110">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16246,9 +16479,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0755075B-2E65-410D-A27F-07A269EC3FA7}">
   <dimension ref="A1:W3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -16319,7 +16552,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -16390,7 +16623,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>158</v>
       </c>
@@ -16469,15 +16702,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865B2AF4-2CF4-4093-8D70-C931333F20A4}">
   <dimension ref="A1:AF7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.42578125" customWidth="1"/>
-    <col min="25" max="25" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="24.453125" customWidth="1"/>
+    <col min="25" max="25" width="20.7265625" customWidth="1"/>
     <col min="32" max="32" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>159</v>
       </c>
@@ -16575,7 +16808,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -16673,7 +16906,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>187</v>
       </c>
@@ -16771,7 +17004,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>191</v>
       </c>
@@ -16869,7 +17102,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>193</v>
       </c>
@@ -16967,7 +17200,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>194</v>
       </c>
@@ -17065,7 +17298,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>196</v>
       </c>
@@ -17165,12 +17398,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E3:AE7">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q3:AE3 B3:E7 I3:M7 Q4:S4 W4:X4 AC4:AE4 N5:AE5 Q6:AE6 Q7:S7 W7:X7 AC7:AE7">
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17181,16 +17414,22 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA691ACA-93ED-4815-AE98-5327707E2A32}">
-  <dimension ref="A1:AO30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AR31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.140625" customWidth="1"/>
+    <col min="1" max="1" width="38.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="25.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>198</v>
       </c>
@@ -17207,115 +17446,124 @@
         <v>198</v>
       </c>
       <c r="F1" t="s">
+        <v>376</v>
+      </c>
+      <c r="G1" t="s">
         <v>199</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>200</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>201</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>378</v>
+      </c>
+      <c r="K1" t="s">
         <v>202</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>203</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>204</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
+        <v>379</v>
+      </c>
+      <c r="O1" t="s">
         <v>205</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>206</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>186</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>185</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>163</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>164</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>172</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>165</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>166</v>
       </c>
-      <c r="U1" t="s">
+      <c r="X1" t="s">
         <v>207</v>
       </c>
-      <c r="V1" t="s">
+      <c r="Y1" t="s">
         <v>208</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Z1" t="s">
         <v>209</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AA1" t="s">
         <v>210</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AB1" t="s">
         <v>211</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AC1" t="s">
         <v>212</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AD1" t="s">
         <v>213</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AE1" t="s">
         <v>214</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AF1" t="s">
         <v>215</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AG1" t="s">
         <v>216</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AH1" t="s">
         <v>217</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AI1" t="s">
         <v>218</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AJ1" t="s">
         <v>219</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AK1" t="s">
         <v>220</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AL1" t="s">
         <v>221</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AM1" t="s">
         <v>222</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AN1" t="s">
         <v>223</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AO1" t="s">
         <v>224</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AP1" t="s">
         <v>225</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AQ1" t="s">
         <v>226</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AR1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -17439,8 +17687,17 @@
       <c r="AO2" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP2" t="s">
+        <v>356</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>356</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="3" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>228</v>
       </c>
@@ -17456,12 +17713,12 @@
       <c r="E3" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="15">
+        <v>0</v>
+      </c>
+      <c r="G3" s="8">
         <v>0.92</v>
       </c>
-      <c r="G3" s="15">
-        <v>0</v>
-      </c>
       <c r="H3" s="15">
         <v>0</v>
       </c>
@@ -17474,33 +17731,33 @@
       <c r="K3" s="15">
         <v>0</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="15">
+        <v>0</v>
+      </c>
+      <c r="M3" s="15">
+        <v>0</v>
+      </c>
+      <c r="N3" s="15">
+        <v>0</v>
+      </c>
+      <c r="O3" s="8">
         <v>317</v>
       </c>
-      <c r="M3" s="15">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" s="16">
+      <c r="P3" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3" s="16">
         <v>500</v>
       </c>
-      <c r="P3" s="8">
+      <c r="S3" s="8">
         <v>75</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="T3" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
         <v>0</v>
       </c>
@@ -17564,8 +17821,17 @@
       <c r="AO3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>231</v>
       </c>
@@ -17581,11 +17847,11 @@
       <c r="E4" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F4" s="13">
-        <v>1</v>
-      </c>
-      <c r="G4" s="15">
-        <v>0</v>
+      <c r="F4" s="15">
+        <v>0</v>
+      </c>
+      <c r="G4" s="13">
+        <v>1</v>
       </c>
       <c r="H4" s="15">
         <v>0</v>
@@ -17599,33 +17865,33 @@
       <c r="K4" s="15">
         <v>0</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="15">
+        <v>0</v>
+      </c>
+      <c r="M4" s="15">
+        <v>0</v>
+      </c>
+      <c r="N4" s="15">
+        <v>0</v>
+      </c>
+      <c r="O4" s="13">
         <v>1000</v>
       </c>
-      <c r="M4" s="15">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" s="16">
+      <c r="P4" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4" s="16">
         <v>1000</v>
       </c>
-      <c r="P4" s="13">
+      <c r="S4" s="13">
         <v>1000</v>
       </c>
-      <c r="Q4" s="16">
+      <c r="T4" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R4" s="11">
-        <v>0</v>
-      </c>
-      <c r="S4" s="11">
-        <v>0</v>
-      </c>
-      <c r="T4" s="11">
-        <v>0</v>
-      </c>
       <c r="U4" s="11">
         <v>0</v>
       </c>
@@ -17689,8 +17955,17 @@
       <c r="AO4" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP4" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>232</v>
       </c>
@@ -17706,12 +17981,12 @@
       <c r="E5" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="15">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8">
         <v>0.92</v>
       </c>
-      <c r="G5" s="15">
-        <v>0</v>
-      </c>
       <c r="H5" s="15">
         <v>0</v>
       </c>
@@ -17724,33 +17999,33 @@
       <c r="K5" s="15">
         <v>0</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="15">
+        <v>0</v>
+      </c>
+      <c r="M5" s="15">
+        <v>0</v>
+      </c>
+      <c r="N5" s="15">
+        <v>0</v>
+      </c>
+      <c r="O5" s="8">
         <v>232</v>
       </c>
-      <c r="M5" s="15">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" s="16">
+      <c r="P5" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5" s="16">
         <v>500</v>
       </c>
-      <c r="P5" s="8">
+      <c r="S5" s="8">
         <v>110</v>
       </c>
-      <c r="Q5" s="16">
+      <c r="T5" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
         <v>0</v>
       </c>
@@ -17814,8 +18089,17 @@
       <c r="AO5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:41" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="24" t="s">
         <v>234</v>
       </c>
@@ -17831,12 +18115,12 @@
       <c r="E6" s="24" t="s">
         <v>230</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="15">
+        <v>0</v>
+      </c>
+      <c r="G6" s="24">
         <v>0.92</v>
       </c>
-      <c r="G6" s="24">
-        <v>0</v>
-      </c>
       <c r="H6" s="24">
         <v>0</v>
       </c>
@@ -17850,32 +18134,32 @@
         <v>0</v>
       </c>
       <c r="L6" s="24">
+        <v>0</v>
+      </c>
+      <c r="M6" s="24">
+        <v>0</v>
+      </c>
+      <c r="N6" s="24">
+        <v>0</v>
+      </c>
+      <c r="O6" s="24">
         <v>264</v>
       </c>
-      <c r="M6" s="24">
-        <v>0</v>
-      </c>
-      <c r="N6" s="24">
-        <v>0</v>
-      </c>
-      <c r="O6" s="24">
+      <c r="P6" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="24">
+        <v>0</v>
+      </c>
+      <c r="R6" s="24">
         <v>500</v>
       </c>
-      <c r="P6" s="24">
+      <c r="S6" s="24">
         <v>13</v>
       </c>
-      <c r="Q6" s="24">
+      <c r="T6" s="24">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R6" s="24">
-        <v>0</v>
-      </c>
-      <c r="S6" s="24">
-        <v>0</v>
-      </c>
-      <c r="T6" s="24">
-        <v>0</v>
-      </c>
       <c r="U6" s="24">
         <v>0</v>
       </c>
@@ -17939,8 +18223,17 @@
       <c r="AO6" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP6" s="24">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="24">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>235</v>
       </c>
@@ -17956,11 +18249,11 @@
       <c r="E7" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F7" s="13">
-        <v>1</v>
-      </c>
-      <c r="G7" s="15">
-        <v>0</v>
+      <c r="F7" s="15">
+        <v>0</v>
+      </c>
+      <c r="G7" s="13">
+        <v>1</v>
       </c>
       <c r="H7" s="15">
         <v>0</v>
@@ -17974,33 +18267,33 @@
       <c r="K7" s="15">
         <v>0</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="15">
+        <v>0</v>
+      </c>
+      <c r="M7" s="15">
+        <v>0</v>
+      </c>
+      <c r="N7" s="15">
+        <v>0</v>
+      </c>
+      <c r="O7" s="13">
         <v>1000</v>
       </c>
-      <c r="M7" s="15">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" s="16">
+      <c r="P7" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="16">
         <v>1000</v>
       </c>
-      <c r="P7" s="13">
+      <c r="S7" s="13">
         <v>1000</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="T7" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R7" s="11">
-        <v>0</v>
-      </c>
-      <c r="S7" s="11">
-        <v>0</v>
-      </c>
-      <c r="T7" s="11">
-        <v>0</v>
-      </c>
       <c r="U7" s="11">
         <v>0</v>
       </c>
@@ -18064,8 +18357,17 @@
       <c r="AO7" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP7" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>237</v>
       </c>
@@ -18081,12 +18383,12 @@
       <c r="E8" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="15">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8">
         <v>0.92</v>
       </c>
-      <c r="G8" s="15">
-        <v>0</v>
-      </c>
       <c r="H8" s="15">
         <v>0</v>
       </c>
@@ -18099,33 +18401,33 @@
       <c r="K8" s="15">
         <v>0</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="15">
+        <v>0</v>
+      </c>
+      <c r="M8" s="15">
+        <v>0</v>
+      </c>
+      <c r="N8" s="15">
+        <v>0</v>
+      </c>
+      <c r="O8" s="8">
         <v>232</v>
       </c>
-      <c r="M8" s="15">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" s="16">
+      <c r="P8" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="16">
         <v>500</v>
       </c>
-      <c r="P8" s="8">
+      <c r="S8" s="8">
         <v>110</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="T8" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
         <v>0</v>
       </c>
@@ -18189,8 +18491,17 @@
       <c r="AO8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>238</v>
       </c>
@@ -18206,11 +18517,11 @@
       <c r="E9" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F9" s="8">
-        <v>1</v>
-      </c>
-      <c r="G9" s="15">
-        <v>0</v>
+      <c r="F9" s="15">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8">
+        <v>1</v>
       </c>
       <c r="H9" s="15">
         <v>0</v>
@@ -18224,33 +18535,33 @@
       <c r="K9" s="15">
         <v>0</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="15">
+        <v>0</v>
+      </c>
+      <c r="M9" s="15">
+        <v>0</v>
+      </c>
+      <c r="N9" s="15">
+        <v>0</v>
+      </c>
+      <c r="O9" s="8">
         <v>5</v>
       </c>
-      <c r="M9" s="15">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" s="16">
+      <c r="P9" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="16">
         <v>500</v>
       </c>
-      <c r="P9" s="8">
+      <c r="S9" s="8">
         <v>23</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="T9" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
         <v>0</v>
       </c>
@@ -18314,8 +18625,17 @@
       <c r="AO9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>240</v>
       </c>
@@ -18331,11 +18651,11 @@
       <c r="E10" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F10" s="13">
-        <v>1</v>
-      </c>
-      <c r="G10" s="15">
-        <v>0</v>
+      <c r="F10" s="15">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13">
+        <v>1</v>
       </c>
       <c r="H10" s="15">
         <v>0</v>
@@ -18349,33 +18669,33 @@
       <c r="K10" s="15">
         <v>0</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="15">
+        <v>0</v>
+      </c>
+      <c r="M10" s="15">
+        <v>0</v>
+      </c>
+      <c r="N10" s="15">
+        <v>0</v>
+      </c>
+      <c r="O10" s="13">
         <v>1000</v>
       </c>
-      <c r="M10" s="15">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" s="16">
+      <c r="P10" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10" s="16">
         <v>1000</v>
       </c>
-      <c r="P10" s="13">
+      <c r="S10" s="13">
         <v>1000</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="T10" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R10" s="11">
-        <v>0</v>
-      </c>
-      <c r="S10" s="11">
-        <v>0</v>
-      </c>
-      <c r="T10" s="11">
-        <v>0</v>
-      </c>
       <c r="U10" s="11">
         <v>0</v>
       </c>
@@ -18439,8 +18759,17 @@
       <c r="AO10" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP10" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>241</v>
       </c>
@@ -18456,11 +18785,11 @@
       <c r="E11" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F11" s="13">
-        <v>1</v>
-      </c>
-      <c r="G11" s="15">
-        <v>0</v>
+      <c r="F11" s="15">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13">
+        <v>1</v>
       </c>
       <c r="H11" s="15">
         <v>0</v>
@@ -18474,33 +18803,33 @@
       <c r="K11" s="15">
         <v>0</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="15">
+        <v>0</v>
+      </c>
+      <c r="M11" s="15">
+        <v>0</v>
+      </c>
+      <c r="N11" s="15">
+        <v>0</v>
+      </c>
+      <c r="O11" s="13">
         <v>1000</v>
       </c>
-      <c r="M11" s="15">
-        <v>0</v>
-      </c>
-      <c r="N11" s="11">
-        <v>0</v>
-      </c>
-      <c r="O11" s="16">
+      <c r="P11" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="16">
         <v>1000</v>
       </c>
-      <c r="P11" s="13">
+      <c r="S11" s="13">
         <v>1000</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="T11" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R11" s="11">
-        <v>0</v>
-      </c>
-      <c r="S11" s="11">
-        <v>0</v>
-      </c>
-      <c r="T11" s="11">
-        <v>0</v>
-      </c>
       <c r="U11" s="11">
         <v>0</v>
       </c>
@@ -18564,8 +18893,17 @@
       <c r="AO11" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP11" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>243</v>
       </c>
@@ -18581,11 +18919,11 @@
       <c r="E12" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F12" s="13">
-        <v>1</v>
-      </c>
-      <c r="G12" s="15">
-        <v>0</v>
+      <c r="F12" s="15">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <v>1</v>
       </c>
       <c r="H12" s="15">
         <v>0</v>
@@ -18599,33 +18937,33 @@
       <c r="K12" s="15">
         <v>0</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="15">
+        <v>0</v>
+      </c>
+      <c r="M12" s="15">
+        <v>0</v>
+      </c>
+      <c r="N12" s="15">
+        <v>0</v>
+      </c>
+      <c r="O12" s="13">
         <v>1000</v>
       </c>
-      <c r="M12" s="15">
-        <v>0</v>
-      </c>
-      <c r="N12" s="11">
-        <v>0</v>
-      </c>
-      <c r="O12" s="16">
+      <c r="P12" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0</v>
+      </c>
+      <c r="R12" s="16">
         <v>1000</v>
       </c>
-      <c r="P12" s="13">
+      <c r="S12" s="13">
         <v>1000</v>
       </c>
-      <c r="Q12" s="16">
+      <c r="T12" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R12" s="11">
-        <v>0</v>
-      </c>
-      <c r="S12" s="11">
-        <v>0</v>
-      </c>
-      <c r="T12" s="11">
-        <v>0</v>
-      </c>
       <c r="U12" s="11">
         <v>0</v>
       </c>
@@ -18689,8 +19027,17 @@
       <c r="AO12" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>245</v>
       </c>
@@ -18706,12 +19053,12 @@
       <c r="E13" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="15">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
         <v>0.9</v>
       </c>
-      <c r="G13" s="15">
-        <v>0</v>
-      </c>
       <c r="H13" s="15">
         <v>0</v>
       </c>
@@ -18724,33 +19071,33 @@
       <c r="K13" s="15">
         <v>0</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="15">
+        <v>0</v>
+      </c>
+      <c r="M13" s="15">
+        <v>0</v>
+      </c>
+      <c r="N13" s="15">
+        <v>0</v>
+      </c>
+      <c r="O13" s="8">
         <v>26</v>
       </c>
-      <c r="M13" s="15">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" s="16">
+      <c r="P13" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13" s="16">
         <v>500</v>
       </c>
-      <c r="P13" s="8">
+      <c r="S13" s="8">
         <v>38</v>
       </c>
-      <c r="Q13" s="16">
+      <c r="T13" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
         <v>0</v>
       </c>
@@ -18814,8 +19161,17 @@
       <c r="AO13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>246</v>
       </c>
@@ -18831,12 +19187,12 @@
       <c r="E14" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="15">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8">
         <v>0.89</v>
       </c>
-      <c r="G14" s="15">
-        <v>0</v>
-      </c>
       <c r="H14" s="15">
         <v>0</v>
       </c>
@@ -18849,33 +19205,33 @@
       <c r="K14" s="15">
         <v>0</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="15">
+        <v>0</v>
+      </c>
+      <c r="M14" s="15">
+        <v>0</v>
+      </c>
+      <c r="N14" s="15">
+        <v>0</v>
+      </c>
+      <c r="O14" s="8">
         <v>42</v>
       </c>
-      <c r="M14" s="15">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" s="16">
+      <c r="P14" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14" s="16">
         <v>500</v>
       </c>
-      <c r="P14" s="8">
+      <c r="S14" s="8">
         <v>45</v>
       </c>
-      <c r="Q14" s="16">
+      <c r="T14" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
         <v>0</v>
       </c>
@@ -18939,8 +19295,17 @@
       <c r="AO14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>247</v>
       </c>
@@ -18956,11 +19321,11 @@
       <c r="E15" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F15" s="13">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15">
-        <v>0</v>
+      <c r="F15" s="15">
+        <v>0</v>
+      </c>
+      <c r="G15" s="13">
+        <v>1</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
@@ -18974,33 +19339,33 @@
       <c r="K15" s="15">
         <v>0</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="15">
+        <v>0</v>
+      </c>
+      <c r="M15" s="15">
+        <v>0</v>
+      </c>
+      <c r="N15" s="15">
+        <v>0</v>
+      </c>
+      <c r="O15" s="13">
         <v>1000</v>
       </c>
-      <c r="M15" s="15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" s="16">
+      <c r="P15" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15" s="16">
         <v>1000</v>
       </c>
-      <c r="P15" s="13">
+      <c r="S15" s="13">
         <v>1000</v>
       </c>
-      <c r="Q15" s="16">
+      <c r="T15" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R15" s="11">
-        <v>0</v>
-      </c>
-      <c r="S15" s="11">
-        <v>0</v>
-      </c>
-      <c r="T15" s="11">
-        <v>0</v>
-      </c>
       <c r="U15" s="11">
         <v>0</v>
       </c>
@@ -19064,8 +19429,17 @@
       <c r="AO15" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>248</v>
       </c>
@@ -19081,12 +19455,12 @@
       <c r="E16" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="15">
+        <v>0</v>
+      </c>
+      <c r="G16" s="8">
         <v>0.75</v>
       </c>
-      <c r="G16" s="15">
-        <v>0</v>
-      </c>
       <c r="H16" s="15">
         <v>0</v>
       </c>
@@ -19099,33 +19473,33 @@
       <c r="K16" s="15">
         <v>0</v>
       </c>
-      <c r="L16" s="8">
+      <c r="L16" s="15">
+        <v>0</v>
+      </c>
+      <c r="M16" s="15">
+        <v>0</v>
+      </c>
+      <c r="N16" s="15">
+        <v>0</v>
+      </c>
+      <c r="O16" s="8">
         <v>30.1</v>
       </c>
-      <c r="M16" s="15">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" s="16">
+      <c r="P16" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16" s="16">
         <v>500</v>
       </c>
-      <c r="P16" s="8">
+      <c r="S16" s="8">
         <v>37</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="T16" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R16" s="7">
-        <v>0</v>
-      </c>
-      <c r="S16" s="7">
-        <v>0</v>
-      </c>
-      <c r="T16" s="7">
-        <v>0</v>
-      </c>
       <c r="U16" s="7">
         <v>0</v>
       </c>
@@ -19189,8 +19563,17 @@
       <c r="AO16" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP16" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>250</v>
       </c>
@@ -19206,11 +19589,11 @@
       <c r="E17" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="F17" s="16">
-        <v>1</v>
-      </c>
-      <c r="G17" s="15">
-        <v>0</v>
+      <c r="F17" s="15">
+        <v>0</v>
+      </c>
+      <c r="G17" s="16">
+        <v>1</v>
       </c>
       <c r="H17" s="15">
         <v>0</v>
@@ -19224,57 +19607,57 @@
       <c r="K17" s="15">
         <v>0</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L17" s="15">
+        <v>0</v>
+      </c>
+      <c r="M17" s="15">
+        <v>0</v>
+      </c>
+      <c r="N17" s="15">
+        <v>0</v>
+      </c>
+      <c r="O17" s="8">
         <v>8</v>
       </c>
-      <c r="M17" s="15">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" s="16">
+      <c r="P17" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17" s="16">
         <v>999</v>
       </c>
-      <c r="P17" s="8">
+      <c r="S17" s="8">
         <v>142</v>
       </c>
-      <c r="Q17" s="16">
+      <c r="T17" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17" s="16" t="s">
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="V17" s="16" t="s">
+      <c r="Y17" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17" s="8">
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="8">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Y17" s="8">
+      <c r="AB17" s="8">
         <v>100</v>
       </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
       <c r="AC17">
         <v>0</v>
       </c>
@@ -19314,8 +19697,17 @@
       <c r="AO17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>255</v>
       </c>
@@ -19331,11 +19723,11 @@
       <c r="E18" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="F18" s="16">
-        <v>1</v>
-      </c>
-      <c r="G18" s="15">
-        <v>0</v>
+      <c r="F18" s="15">
+        <v>0</v>
+      </c>
+      <c r="G18" s="16">
+        <v>1</v>
       </c>
       <c r="H18" s="15">
         <v>0</v>
@@ -19349,57 +19741,57 @@
       <c r="K18" s="15">
         <v>0</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="15">
+        <v>0</v>
+      </c>
+      <c r="M18" s="15">
+        <v>0</v>
+      </c>
+      <c r="N18" s="15">
+        <v>0</v>
+      </c>
+      <c r="O18" s="8">
         <v>8</v>
       </c>
-      <c r="M18" s="15">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" s="16">
+      <c r="P18" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18" s="16">
         <v>10000</v>
       </c>
-      <c r="P18" s="8">
+      <c r="S18" s="8">
         <v>40</v>
       </c>
-      <c r="Q18" s="16">
+      <c r="T18" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18" s="16" t="s">
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="V18" s="16" t="s">
+      <c r="Y18" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18" s="8">
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="8">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Y18" s="8">
+      <c r="AB18" s="8">
         <v>100</v>
       </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
       <c r="AC18">
         <v>0</v>
       </c>
@@ -19439,8 +19831,17 @@
       <c r="AO18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:41" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:44" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="24" t="s">
         <v>256</v>
       </c>
@@ -19456,11 +19857,11 @@
       <c r="E19" s="24" t="s">
         <v>252</v>
       </c>
-      <c r="F19" s="24">
-        <v>1</v>
+      <c r="F19" s="15">
+        <v>0</v>
       </c>
       <c r="G19" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="24">
         <v>0</v>
@@ -19475,62 +19876,62 @@
         <v>0</v>
       </c>
       <c r="L19" s="24">
+        <v>0</v>
+      </c>
+      <c r="M19" s="24">
+        <v>0</v>
+      </c>
+      <c r="N19" s="24">
+        <v>0</v>
+      </c>
+      <c r="O19" s="24">
         <v>12</v>
       </c>
-      <c r="M19" s="24">
-        <v>0</v>
-      </c>
-      <c r="N19" s="24">
-        <v>0</v>
-      </c>
-      <c r="O19" s="24">
+      <c r="P19" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="24">
+        <v>0</v>
+      </c>
+      <c r="R19" s="24">
         <v>500</v>
       </c>
-      <c r="P19" s="24">
+      <c r="S19" s="24">
         <v>137</v>
       </c>
-      <c r="Q19" s="24">
+      <c r="T19" s="24">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R19" s="24">
-        <v>0</v>
-      </c>
-      <c r="S19" s="24">
-        <v>0</v>
-      </c>
-      <c r="T19" s="24">
-        <v>0</v>
-      </c>
-      <c r="U19" s="24" t="s">
+      <c r="U19" s="24">
+        <v>0</v>
+      </c>
+      <c r="V19" s="24">
+        <v>0</v>
+      </c>
+      <c r="W19" s="24">
+        <v>0</v>
+      </c>
+      <c r="X19" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="V19" s="24" t="s">
+      <c r="Y19" s="24" t="s">
         <v>258</v>
       </c>
-      <c r="W19" s="24">
-        <v>0</v>
-      </c>
-      <c r="X19" s="24">
+      <c r="Z19" s="24">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="24">
         <v>0.4</v>
       </c>
-      <c r="Y19" s="24">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="24">
+      <c r="AB19" s="24">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="24">
         <v>3</v>
       </c>
-      <c r="AA19" s="24">
+      <c r="AD19" s="24">
         <v>0.8</v>
       </c>
-      <c r="AB19" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="24">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="24">
-        <v>0</v>
-      </c>
       <c r="AE19" s="24">
         <v>0</v>
       </c>
@@ -19564,8 +19965,17 @@
       <c r="AO19" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP19" s="24">
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="24">
+        <v>0</v>
+      </c>
+      <c r="AR19" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>259</v>
       </c>
@@ -19581,11 +19991,11 @@
       <c r="E20" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="F20" s="16">
-        <v>1</v>
-      </c>
-      <c r="G20" s="15">
-        <v>0</v>
+      <c r="F20" s="15">
+        <v>0</v>
+      </c>
+      <c r="G20" s="16">
+        <v>1</v>
       </c>
       <c r="H20" s="15">
         <v>0</v>
@@ -19599,63 +20009,63 @@
       <c r="K20" s="15">
         <v>0</v>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="15">
+        <v>0</v>
+      </c>
+      <c r="M20" s="15">
+        <v>0</v>
+      </c>
+      <c r="N20" s="15">
+        <v>0</v>
+      </c>
+      <c r="O20" s="8">
         <v>12</v>
       </c>
-      <c r="M20" s="15">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" s="16">
+      <c r="P20" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20" s="16">
         <v>10000</v>
       </c>
-      <c r="P20" s="8">
+      <c r="S20" s="8">
         <v>59</v>
       </c>
-      <c r="Q20" s="16">
+      <c r="T20" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20" s="16" t="s">
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="V20" s="16" t="s">
+      <c r="Y20" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20" s="8">
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="8">
         <v>0.4</v>
       </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="8">
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="8">
         <v>3</v>
       </c>
-      <c r="AA20" s="8">
+      <c r="AD20" s="8">
         <v>0.8</v>
       </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
       <c r="AE20">
         <v>0</v>
       </c>
@@ -19689,8 +20099,17 @@
       <c r="AO20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>260</v>
       </c>
@@ -19706,11 +20125,11 @@
       <c r="E21" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="F21" s="16">
-        <v>1</v>
-      </c>
-      <c r="G21" s="15">
-        <v>0</v>
+      <c r="F21" s="15">
+        <v>0</v>
+      </c>
+      <c r="G21" s="16">
+        <v>1</v>
       </c>
       <c r="H21" s="15">
         <v>0</v>
@@ -19724,54 +20143,54 @@
       <c r="K21" s="15">
         <v>0</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="15">
+        <v>0</v>
+      </c>
+      <c r="M21" s="15">
+        <v>0</v>
+      </c>
+      <c r="N21" s="15">
+        <v>0</v>
+      </c>
+      <c r="O21" s="8">
         <v>9</v>
       </c>
-      <c r="M21" s="15">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" s="16">
+      <c r="P21" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21" s="16">
         <v>10000</v>
       </c>
-      <c r="P21" s="8">
+      <c r="S21" s="8">
         <v>72</v>
       </c>
-      <c r="Q21" s="16">
+      <c r="T21" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21" s="16" t="s">
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="V21" s="16" t="s">
+      <c r="Y21" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21" s="8">
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="8">
         <v>0.5</v>
       </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
       <c r="AB21">
         <v>0</v>
       </c>
@@ -19814,8 +20233,17 @@
       <c r="AO21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
         <v>263</v>
       </c>
@@ -19831,11 +20259,11 @@
       <c r="E22" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="F22" s="16">
-        <v>1</v>
-      </c>
-      <c r="G22" s="15">
-        <v>0</v>
+      <c r="F22" s="15">
+        <v>0</v>
+      </c>
+      <c r="G22" s="16">
+        <v>1</v>
       </c>
       <c r="H22" s="15">
         <v>0</v>
@@ -19849,54 +20277,54 @@
       <c r="K22" s="15">
         <v>0</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="15">
+        <v>0</v>
+      </c>
+      <c r="M22" s="15">
+        <v>0</v>
+      </c>
+      <c r="N22" s="15">
+        <v>0</v>
+      </c>
+      <c r="O22" s="13">
         <v>1000</v>
       </c>
-      <c r="M22" s="15">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" s="16">
+      <c r="P22" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22" s="16">
         <v>1000</v>
       </c>
-      <c r="P22" s="13">
+      <c r="S22" s="13">
         <v>1000</v>
       </c>
-      <c r="Q22" s="16">
+      <c r="T22" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R22" s="11">
-        <v>0</v>
-      </c>
-      <c r="S22" s="11">
-        <v>0</v>
-      </c>
-      <c r="T22" s="11">
-        <v>0</v>
-      </c>
-      <c r="U22" s="16" t="s">
+      <c r="U22" s="11">
+        <v>0</v>
+      </c>
+      <c r="V22" s="11">
+        <v>0</v>
+      </c>
+      <c r="W22" s="11">
+        <v>0</v>
+      </c>
+      <c r="X22" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="V22" s="16" t="s">
+      <c r="Y22" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="W22" s="11">
-        <v>0</v>
-      </c>
-      <c r="X22" s="8">
+      <c r="Z22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="8">
         <v>0.5</v>
       </c>
-      <c r="Y22" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="11">
-        <v>0</v>
-      </c>
       <c r="AB22" s="11">
         <v>0</v>
       </c>
@@ -19939,8 +20367,17 @@
       <c r="AO22" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR22" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
         <v>265</v>
       </c>
@@ -19956,11 +20393,11 @@
       <c r="E23" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="F23" s="16">
-        <v>1</v>
-      </c>
-      <c r="G23" s="15">
-        <v>0</v>
+      <c r="F23" s="15">
+        <v>0</v>
+      </c>
+      <c r="G23" s="16">
+        <v>1</v>
       </c>
       <c r="H23" s="15">
         <v>0</v>
@@ -19974,53 +20411,53 @@
       <c r="K23" s="15">
         <v>0</v>
       </c>
-      <c r="L23" s="13">
+      <c r="L23" s="15">
+        <v>0</v>
+      </c>
+      <c r="M23" s="15">
+        <v>0</v>
+      </c>
+      <c r="N23" s="15">
+        <v>0</v>
+      </c>
+      <c r="O23" s="13">
         <v>1000</v>
       </c>
-      <c r="M23" s="15">
-        <v>0</v>
-      </c>
-      <c r="N23" s="11">
-        <v>0</v>
-      </c>
-      <c r="O23" s="16">
+      <c r="P23" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="11">
+        <v>0</v>
+      </c>
+      <c r="R23" s="16">
         <v>10000</v>
       </c>
-      <c r="P23" s="13">
+      <c r="S23" s="13">
         <v>1000</v>
       </c>
-      <c r="Q23" s="16">
+      <c r="T23" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R23" s="11">
-        <v>0</v>
-      </c>
-      <c r="S23" s="11">
-        <v>0</v>
-      </c>
-      <c r="T23" s="11">
-        <v>0</v>
-      </c>
-      <c r="U23" s="16" t="s">
+      <c r="U23" s="11">
+        <v>0</v>
+      </c>
+      <c r="V23" s="11">
+        <v>0</v>
+      </c>
+      <c r="W23" s="11">
+        <v>0</v>
+      </c>
+      <c r="X23" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="V23" s="16" t="s">
+      <c r="Y23" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="W23" s="11">
-        <v>0</v>
-      </c>
-      <c r="X23" s="8">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="11">
-        <v>0</v>
-      </c>
       <c r="Z23" s="11">
         <v>0</v>
       </c>
-      <c r="AA23" s="11">
-        <v>0</v>
+      <c r="AA23" s="8">
+        <v>1</v>
       </c>
       <c r="AB23" s="11">
         <v>0</v>
@@ -20064,8 +20501,17 @@
       <c r="AO23" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR23" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>268</v>
       </c>
@@ -20082,14 +20528,14 @@
         <v>230</v>
       </c>
       <c r="F24" s="8">
+        <v>0</v>
+      </c>
+      <c r="G24" s="8">
         <v>0.375</v>
       </c>
-      <c r="G24" s="8">
+      <c r="H24" s="8">
         <v>0.57499999999999996</v>
       </c>
-      <c r="H24" s="15">
-        <v>0</v>
-      </c>
       <c r="I24" s="15">
         <v>0</v>
       </c>
@@ -20099,33 +20545,33 @@
       <c r="K24" s="15">
         <v>0</v>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="15">
+        <v>0</v>
+      </c>
+      <c r="M24" s="15">
+        <v>0</v>
+      </c>
+      <c r="N24" s="15">
+        <v>0</v>
+      </c>
+      <c r="O24" s="8">
         <v>347</v>
       </c>
-      <c r="M24" s="8">
+      <c r="P24" s="8">
         <v>225</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24" s="16">
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24" s="16">
         <v>10000</v>
       </c>
-      <c r="P24" s="8">
+      <c r="S24" s="8">
         <v>129</v>
       </c>
-      <c r="Q24" s="16">
+      <c r="T24" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
       <c r="U24">
         <v>0</v>
       </c>
@@ -20189,8 +20635,17 @@
       <c r="AO24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>270</v>
       </c>
@@ -20207,14 +20662,14 @@
         <v>230</v>
       </c>
       <c r="F25" s="8">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8">
         <v>0.39</v>
       </c>
-      <c r="G25" s="8">
+      <c r="H25" s="8">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H25" s="15">
-        <v>0</v>
-      </c>
       <c r="I25" s="15">
         <v>0</v>
       </c>
@@ -20224,33 +20679,33 @@
       <c r="K25" s="15">
         <v>0</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="15">
+        <v>0</v>
+      </c>
+      <c r="M25" s="15">
+        <v>0</v>
+      </c>
+      <c r="N25" s="15">
+        <v>0</v>
+      </c>
+      <c r="O25" s="8">
         <v>140</v>
       </c>
-      <c r="M25" s="8">
+      <c r="P25" s="8">
         <v>97</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" s="16">
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25" s="16">
         <v>10000</v>
       </c>
-      <c r="P25" s="8">
+      <c r="S25" s="8">
         <v>130</v>
       </c>
-      <c r="Q25" s="16">
+      <c r="T25" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
       <c r="U25">
         <v>0</v>
       </c>
@@ -20314,8 +20769,17 @@
       <c r="AO25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>272</v>
       </c>
@@ -20332,14 +20796,14 @@
         <v>230</v>
       </c>
       <c r="F26" s="8">
+        <v>0</v>
+      </c>
+      <c r="G26" s="8">
         <v>0.35</v>
       </c>
-      <c r="G26" s="8">
+      <c r="H26" s="8">
         <v>0.6</v>
       </c>
-      <c r="H26" s="15">
-        <v>0</v>
-      </c>
       <c r="I26" s="15">
         <v>0</v>
       </c>
@@ -20349,33 +20813,33 @@
       <c r="K26" s="15">
         <v>0</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="15">
+        <v>0</v>
+      </c>
+      <c r="M26" s="15">
+        <v>0</v>
+      </c>
+      <c r="N26" s="15">
+        <v>0</v>
+      </c>
+      <c r="O26" s="8">
         <v>95</v>
       </c>
-      <c r="M26" s="8">
+      <c r="P26" s="8">
         <v>55</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" s="16">
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26" s="16">
         <v>10000</v>
       </c>
-      <c r="P26" s="8">
+      <c r="S26" s="8">
         <v>765</v>
       </c>
-      <c r="Q26" s="16">
+      <c r="T26" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
       <c r="U26">
         <v>0</v>
       </c>
@@ -20439,8 +20903,17 @@
       <c r="AO26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>274</v>
       </c>
@@ -20457,14 +20930,14 @@
         <v>230</v>
       </c>
       <c r="F27" s="8">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8">
         <v>0.35</v>
       </c>
-      <c r="G27" s="8">
+      <c r="H27" s="8">
         <v>0.6</v>
       </c>
-      <c r="H27" s="15">
-        <v>0</v>
-      </c>
       <c r="I27" s="15">
         <v>0</v>
       </c>
@@ -20474,33 +20947,33 @@
       <c r="K27" s="15">
         <v>0</v>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="15">
+        <v>0</v>
+      </c>
+      <c r="M27" s="15">
+        <v>0</v>
+      </c>
+      <c r="N27" s="15">
+        <v>0</v>
+      </c>
+      <c r="O27" s="8">
         <v>95</v>
       </c>
-      <c r="M27" s="8">
+      <c r="P27" s="8">
         <v>55</v>
       </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" s="16">
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27" s="16">
         <v>10000</v>
       </c>
-      <c r="P27" s="8">
+      <c r="S27" s="8">
         <v>765</v>
       </c>
-      <c r="Q27" s="16">
+      <c r="T27" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
       <c r="U27">
         <v>0</v>
       </c>
@@ -20564,8 +21037,17 @@
       <c r="AO27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP27">
+        <v>0</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>276</v>
       </c>
@@ -20579,12 +21061,12 @@
       <c r="E28" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="15">
+        <v>0</v>
+      </c>
+      <c r="G28" s="8">
         <v>0.78500000000000003</v>
       </c>
-      <c r="G28" s="15">
-        <v>0</v>
-      </c>
       <c r="H28" s="15">
         <v>0</v>
       </c>
@@ -20597,33 +21079,33 @@
       <c r="K28" s="15">
         <v>0</v>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="15">
+        <v>0</v>
+      </c>
+      <c r="M28" s="15">
+        <v>0</v>
+      </c>
+      <c r="N28" s="15">
+        <v>0</v>
+      </c>
+      <c r="O28" s="8">
         <v>1.3</v>
       </c>
-      <c r="M28" s="15">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28" s="16">
+      <c r="P28" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28" s="16">
         <v>10000</v>
       </c>
-      <c r="P28" s="8">
+      <c r="S28" s="8">
         <v>77</v>
       </c>
-      <c r="Q28" s="16">
+      <c r="T28" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
       <c r="U28">
         <v>0</v>
       </c>
@@ -20687,8 +21169,17 @@
       <c r="AO28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>277</v>
       </c>
@@ -20702,12 +21193,12 @@
       <c r="E29" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="15">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
         <v>0.83</v>
       </c>
-      <c r="G29" s="15">
-        <v>0</v>
-      </c>
       <c r="H29" s="15">
         <v>0</v>
       </c>
@@ -20720,33 +21211,33 @@
       <c r="K29" s="15">
         <v>0</v>
       </c>
-      <c r="L29" s="8">
+      <c r="L29" s="15">
+        <v>0</v>
+      </c>
+      <c r="M29" s="15">
+        <v>0</v>
+      </c>
+      <c r="N29" s="15">
+        <v>0</v>
+      </c>
+      <c r="O29" s="8">
         <v>10</v>
       </c>
-      <c r="M29" s="15">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29" s="16">
+      <c r="P29" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29" s="16">
         <v>10000</v>
       </c>
-      <c r="P29" s="8">
+      <c r="S29" s="8">
         <v>67</v>
       </c>
-      <c r="Q29" s="16">
+      <c r="T29" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
       <c r="U29">
         <v>0</v>
       </c>
@@ -20810,8 +21301,17 @@
       <c r="AO29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>278</v>
       </c>
@@ -20828,14 +21328,14 @@
         <v>230</v>
       </c>
       <c r="F30" s="8">
+        <v>0</v>
+      </c>
+      <c r="G30" s="8">
         <v>0.4</v>
       </c>
-      <c r="G30" s="8">
+      <c r="H30" s="8">
         <v>0.5</v>
       </c>
-      <c r="H30" s="15">
-        <v>0</v>
-      </c>
       <c r="I30" s="15">
         <v>0</v>
       </c>
@@ -20845,33 +21345,33 @@
       <c r="K30" s="15">
         <v>0</v>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="15">
+        <v>0</v>
+      </c>
+      <c r="M30" s="15">
+        <v>0</v>
+      </c>
+      <c r="N30" s="15">
+        <v>0</v>
+      </c>
+      <c r="O30" s="8">
         <v>10</v>
       </c>
-      <c r="M30" s="13">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30" s="16">
+      <c r="P30" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30" s="16">
         <v>10000</v>
       </c>
-      <c r="P30" s="8">
+      <c r="S30" s="8">
         <v>480</v>
       </c>
-      <c r="Q30" s="16">
+      <c r="T30" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
       <c r="U30">
         <v>0</v>
       </c>
@@ -20933,62 +21433,225 @@
         <v>0</v>
       </c>
       <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>0</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>373</v>
+      </c>
+      <c r="B31" s="16">
+        <v>1</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="F31" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="H31" s="8">
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="I31" s="15">
+        <v>0</v>
+      </c>
+      <c r="J31" s="15">
+        <v>0</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0</v>
+      </c>
+      <c r="L31" s="15">
+        <v>0</v>
+      </c>
+      <c r="M31" s="15">
+        <v>0</v>
+      </c>
+      <c r="N31" s="15">
+        <v>0</v>
+      </c>
+      <c r="O31" s="8">
+        <v>347</v>
+      </c>
+      <c r="P31" s="13">
+        <v>225</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31" s="16">
+        <v>10000</v>
+      </c>
+      <c r="S31" s="8">
+        <v>129</v>
+      </c>
+      <c r="T31" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+      <c r="AN31">
+        <v>0</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>0</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B23:E30">
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="22" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="19" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="18" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:AO30">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+  <conditionalFormatting sqref="G3:AR30">
+    <cfRule type="cellIs" dxfId="27" priority="17" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N30">
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+  <conditionalFormatting sqref="Q4:Q31">
+    <cfRule type="cellIs" dxfId="26" priority="27" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:O3">
-    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
+  <conditionalFormatting sqref="Q3:R3">
+    <cfRule type="cellIs" dxfId="25" priority="26" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O8:O9 B8:E9">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+  <conditionalFormatting sqref="R8:R9 B8:E9">
+    <cfRule type="cellIs" dxfId="24" priority="25" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O13:O14 R13:W21 AB13:AO21 O16:O21 B13:E21">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+  <conditionalFormatting sqref="R13:R14 U13:Z21 AE13:AR21 R16:R21 B13:E21">
+    <cfRule type="cellIs" dxfId="23" priority="23" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O23:O30 R23:W30 AB23:AO30">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+  <conditionalFormatting sqref="R23:R31 U23:Z31 AE23:AR31">
+    <cfRule type="cellIs" dxfId="22" priority="21" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:AO6 O5:O6 R8:AO9 X13:AA16 Y19:Y21 Z21:AA21 Y23 X24:AA30 B3:E6">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+  <conditionalFormatting sqref="U3:AR6 R5:R6 U8:AR9 AA13:AD16 AB19:AB21 AC21:AD21 AB23 AA24:AD30 B3:E6">
+    <cfRule type="cellIs" dxfId="21" priority="20" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z17:AA18">
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
+  <conditionalFormatting sqref="AC17:AD18">
+    <cfRule type="cellIs" dxfId="20" priority="24" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F31">
+    <cfRule type="cellIs" dxfId="13" priority="9" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:E31">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G31:AR31">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA31:AD31">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20999,12 +21662,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{062F9C9F-EC6B-45A0-B400-3E864B701D31}">
   <dimension ref="A1:AA8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>280</v>
       </c>
@@ -21087,7 +21750,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -21170,7 +21833,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>292</v>
       </c>
@@ -21253,7 +21916,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>294</v>
       </c>
@@ -21336,7 +21999,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>295</v>
       </c>
@@ -21419,7 +22082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>296</v>
       </c>
@@ -21502,7 +22165,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>297</v>
       </c>
@@ -21585,7 +22248,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>298</v>
       </c>
@@ -21675,13 +22338,13 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F7A117-64AB-4955-A232-50A2E399D809}">
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="58.42578125" customWidth="1"/>
+    <col min="1" max="1" width="58.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>299</v>
       </c>
@@ -21728,7 +22391,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -21775,7 +22438,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>302</v>
       </c>
@@ -21822,7 +22485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>304</v>
       </c>
@@ -21869,7 +22532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>305</v>
       </c>
@@ -21916,7 +22579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>306</v>
       </c>
@@ -21963,7 +22626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>307</v>
       </c>
@@ -22010,7 +22673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>308</v>
       </c>
@@ -22057,7 +22720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>309</v>
       </c>
@@ -22104,7 +22767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>310</v>
       </c>
@@ -22151,7 +22814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>311</v>
       </c>
@@ -22198,7 +22861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>312</v>
       </c>
@@ -22245,7 +22908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>313</v>
       </c>
@@ -22292,7 +22955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>314</v>
       </c>
@@ -22339,7 +23002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>315</v>
       </c>
@@ -22386,7 +23049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
         <v>316</v>
       </c>
@@ -22433,7 +23096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
         <v>317</v>
       </c>
@@ -22480,7 +23143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
         <v>318</v>
       </c>
@@ -22527,7 +23190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
         <v>319</v>
       </c>
@@ -22574,7 +23237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
         <v>320</v>
       </c>
@@ -22621,7 +23284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>321</v>
       </c>
@@ -22665,6 +23328,53 @@
         <v>0</v>
       </c>
       <c r="O21" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="B22" s="16">
+        <v>1</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="D22" s="16">
+        <v>1</v>
+      </c>
+      <c r="E22" s="16">
+        <v>0</v>
+      </c>
+      <c r="F22" s="16">
+        <v>0</v>
+      </c>
+      <c r="G22" s="16">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16">
+        <v>9999</v>
+      </c>
+      <c r="I22" s="16">
+        <v>0</v>
+      </c>
+      <c r="J22" s="16">
+        <v>0</v>
+      </c>
+      <c r="K22" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="L22" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M22" s="16">
+        <v>0</v>
+      </c>
+      <c r="N22" s="16">
+        <v>0</v>
+      </c>
+      <c r="O22" s="16">
         <v>0</v>
       </c>
     </row>
